--- a/data/config/gui/_Localizations.xlsx
+++ b/data/config/gui/_Localizations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\Anno 1800\mods\[Addon] Return to the Orient\data\config\gui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067D1CE3-5937-4E89-AEAF-9C81F85D17F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471CE549-B700-4896-9980-983CB1C27B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6360" yWindow="3555" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Localization" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3950" uniqueCount="2268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4015" uniqueCount="2317">
   <si>
     <t>GUID</t>
   </si>
@@ -5610,9 +5610,6 @@
     <t>A7_QuestExpedition</t>
   </si>
   <si>
-    <t>Lady Jane's Arctic Appeal</t>
-  </si>
-  <si>
     <t>1404000801</t>
   </si>
   <si>
@@ -6841,6 +6838,156 @@
   </si>
   <si>
     <t>Vous ne pensez pas que les gens comme moi méritent plus que ce que vous offrez?</t>
+  </si>
+  <si>
+    <t>A strange looking letter was just delivered by Madame Kahina. It is an invitation by the sultan, who has heard of your reputation in settling in even the most difficult places in the known world. He requests you to visit him in the capitol of the sultanate; Madam Kahina thinks it could be a lucrative business opportunity and a way to expand you trade empire. This new adventure into the unknown beyond enbesa seems it could be as difficult as it is potentially rewarding.</t>
+  </si>
+  <si>
+    <t>After a long and arduous journey you finally made it to the promised archipelago. The islands contain barely anything but sand and rocks, just a few dry palm trees. To permanently live here and build a city you need nomads, who have lived in deserts like this for centuries and have the knowledge on how to survive here.</t>
+  </si>
+  <si>
+    <t>With so many nomads staying here, you need to start producing food, but barely anything is growing in dry and hot sand. Nomads have traditionally used Norias to pump water from deep underground to water their fields. However too many Norias in one place will drain the aquifiers until there is nothing more to pump. To prevent this, nomads figured out a minimum distance between noria, that guarantees a continuous and sustainable water supply.</t>
+  </si>
+  <si>
+    <t>You have proven yourself worthy of receiving the first envoys of the sultanate who will arrive shortly. They have connections to the sultan and will report of all your successes and failures. As part of the sultan's court they are used to many luxuries of the orient that they will also expect in your city.</t>
+  </si>
+  <si>
+    <t>The work of envoys is long and hard, and diplomatic tasks often consist of a lot of bureaucracy. A consulate offers a well staffed and secure workspace for many envoys, improving their efficiency. The paperwork generated in these buildings can be used to build monumental buildings, host special events and resettle more envoys that can do even more paperwork.</t>
+  </si>
+  <si>
+    <t>More envoys want to move to your emerging city and are demanding, that you build more houses for them. For the city to become become a major hub for cultural exchange it must grow and not only produce a wide range of local wares but also new wares from the Old World and New World.</t>
+  </si>
+  <si>
+    <t>Bazaars have been an integral part of the culture and these marketstalls combine tradition and modernity to let envoys sample the new wares of the industrial age. Envoys are very interested in researching them and will report back to the sultanate, possibly open up new markets for your wares. The only problem for you is to supply the products from so far away.</t>
+  </si>
+  <si>
+    <t>Your city has become very popular within envoy circles, rumor has it, that it is on its way to rival the capitol in size and amenities. A new wave of envoys of the highest rangs in the country is on its way, the east and west are coming closer together than they have ever been in the last 400 years.</t>
+  </si>
+  <si>
+    <t>The sultan is very happy with your development and has granted you access to a blueprint for a monument that will be your crowning achievement in this desert. Only one other Grand Mosque like this has ever been build, centuries ago and building a second one will symbolize that traditions can endure in the rapidly changing industrial age. Not to mention the pilgrimages to the city that will take place and the political influence this will bring you.</t>
+  </si>
+  <si>
+    <t>To start the expedition, go to the World Map and select the Orient Expedition.</t>
+  </si>
+  <si>
+    <t>Build residences and fulfil your Nomads' needs to grow your settlement.</t>
+  </si>
+  <si>
+    <t>Fulfil all your Nomads' needs, and then upgrade any fully-occupied residence to Envoys.</t>
+  </si>
+  <si>
+    <t>Norias can only be constructed at a certain distance to each other..</t>
+  </si>
+  <si>
+    <t>Consulates with envoys in their radius create Sultan's Seals that can be used as lifestyle need for envoys and more things later.</t>
+  </si>
+  <si>
+    <t>If a marketstall is supplied with their ware they start to fulfill luxury needs of envoys, which will generate research points.</t>
+  </si>
+  <si>
+    <t>This monument allows you to carry out pilgrimages, these will increase your influence in the sultanate.</t>
+  </si>
+  <si>
+    <t>An Invitation from the Sultan</t>
+  </si>
+  <si>
+    <t>The People of the Desert</t>
+  </si>
+  <si>
+    <t>An Oasis out of Nothing</t>
+  </si>
+  <si>
+    <t>Cultural Exchange</t>
+  </si>
+  <si>
+    <t>Diplomacy and Paperwork</t>
+  </si>
+  <si>
+    <t>Arrival of Curious Minds</t>
+  </si>
+  <si>
+    <t>A Metropolis Built on Sand</t>
+  </si>
+  <si>
+    <t>A Monument for Eternity</t>
+  </si>
+  <si>
+    <t>Making New Contacts</t>
+  </si>
+  <si>
+    <t>Eine Einladung des Sultans</t>
+  </si>
+  <si>
+    <t>Die Menschen der Wüste</t>
+  </si>
+  <si>
+    <t>Eine Oase aus dem Nichts</t>
+  </si>
+  <si>
+    <t>Neue Kontakte knüpfen</t>
+  </si>
+  <si>
+    <t>Diplomatie und Bürokratie</t>
+  </si>
+  <si>
+    <t>Ankunft neugieriger Geister</t>
+  </si>
+  <si>
+    <t>Kultureller Austausch</t>
+  </si>
+  <si>
+    <t>Eine Metropole auf Sand erbaut</t>
+  </si>
+  <si>
+    <t>Ein Monument für die Ewigkeit</t>
+  </si>
+  <si>
+    <t>Ein seltsam aussehender Brief wurde soeben von Madame Kahina überbracht. Es handelt sich um eine Einladung des Sultans, der von Ihrem Ruf gehört hat, sich selbst an den schwierigsten Orten der bekannten Welt anzusiedeln. Er bittet Sie, ihn in der Hauptstadt des Sultanats zu besuchen; Madame Kahina sieht darin eine lukrative Geschäftsmöglichkeit und eine Chance, Ihr Handelsimperium zu erweitern. Dieses neue Abenteuer ins Unbekannte jenseits von Enbesa scheint ebenso schwierig wie lohnend zu sein.</t>
+  </si>
+  <si>
+    <t>Nach einer langen und beschwerlichen Reise haben Sie endlich den versprochenen Archipel erreicht. Die Inseln bestehen fast nur aus Sand und Felsen, lediglich einige wenige trockene Palmen. Um sich hier dauerhaft niederzulassen und eine Stadt zu errichten, benötigen Sie Nomaden, die seit Jahrhunderten in solchen Wüsten leben und über das nötige Wissen verfügen, um hier zu überleben.</t>
+  </si>
+  <si>
+    <t>Da sich nun so viele Nomaden hier aufhalten, müssen Sie mit der Nahrungsmittelproduktion beginnen, doch im trockenen und heißen Sand wächst kaum etwas. Traditionell nutzen Nomaden Norias, um Wasser aus der Tiefe zu pumpen und ihre Felder zu bewässern. Zu viele Norias an einem Ort würden die Grundwasserleiter jedoch so weit austrocknen, dass nichts mehr gepumpt werden kann. Um dies zu verhindern, ermittelten Nomaden einen Mindestabstand zwischen den Norias, der eine kontinuierliche und nachhaltige Wasserversorgung gewährleistet.</t>
+  </si>
+  <si>
+    <t>Ihr habt euch als würdig erwiesen, die ersten Gesandten des Sultanats zu empfangen, die in Kürze eintreffen werden. Sie stehen in Verbindung mit dem Sultan und werden über all eure Erfolge und Misserfolge berichten. Als Teil des Sultanshofs sind sie an viele Annehmlichkeiten des Orients gewöhnt, die sie auch in eurer Stadt erwarten werden.</t>
+  </si>
+  <si>
+    <t>Die Arbeit der Gesandten ist langwierig und anstrengend, und diplomatische Aufgaben sind oft mit viel Bürokratie verbunden. Ein Konsulat bietet vielen Gesandten einen gut besetzten und sicheren Arbeitsplatz und steigert so ihre Effizienz. Die in diesen Gebäuden anfallenden Dokumente können für den Bau monumentaler Gebäude, die Ausrichtung besonderer Veranstaltungen und die Ansiedlung weiterer Gesandter genutzt werden, die wiederum noch mehr Bürokratie erledigen können.</t>
+  </si>
+  <si>
+    <t>Immer mehr Gesandte möchten in eure aufstrebende Stadt ziehen und fordern, dass ihr mehr Häuser für sie baut. Damit die Stadt zu einem bedeutenden Zentrum des kulturellen Austauschs wird, muss sie wachsen und nicht nur eine breite Palette lokaler Waren, sondern auch neue Produkte aus der Alten und Neuen Welt anbieten.</t>
+  </si>
+  <si>
+    <t>Basare sind seit jeher fester Bestandteil der Kultur. An diesen Marktständen vereinen sich Tradition und Moderne, sodass Gesandte die neuen Waren des Industriezeitalters kennenlernen können. Die Gesandten sind sehr daran interessiert, diese zu erforschen und berichten dem Sultanat darüber, wodurch sich möglicherweise neue Märkte für Ihre Waren erschließen. Die einzige Herausforderung für Sie besteht darin, die Produkte aus so großer Entfernung zu liefern.</t>
+  </si>
+  <si>
+    <t>Ihre Stadt erfreut sich großer Beliebtheit in Gesandtenkreisen. Man munkelt, sie sei auf dem besten Weg, der Hauptstadt in Größe und Ausstattung Konkurrenz zu machen. Eine neue Welle hochrangiger Gesandter des Landes ist im Anmarsch. Ost und West rücken näher zusammen als je zuvor in den letzten 400 Jahren.</t>
+  </si>
+  <si>
+    <t>Der Sultan ist sehr zufrieden mit Ihrer Entwicklung und hat Ihnen Zugang zu den Bauplänen für ein Monument gewährt, das Ihr Meisterwerk in dieser Wüste sein wird. Nur eine weitere Große Moschee dieser Art wurde jemals erbaut, und zwar vor Jahrhunderten. Der Bau einer zweiten symbolisiert, dass Traditionen im sich rasant verändernden Industriezeitalter fortbestehen können. Ganz zu schweigen von den Pilgerfahrten in die Stadt und dem damit verbundenen politischen Einfluss.</t>
+  </si>
+  <si>
+    <t>Um die Expedition zu starten, wählen Sie auf der Weltkarte die Orient-Expedition aus.</t>
+  </si>
+  <si>
+    <t>Errichten Sie Residenzen und erfüllen Sie die Bedürfnisse Ihrer Nomaden, um Ihre Siedlung auszubauen.</t>
+  </si>
+  <si>
+    <t>Erfüllen Sie alle Bedürfnisse Ihrer Nomaden und werten Sie dann jede voll belegte Residenz zu einer Gesandtenresidenz auf.</t>
+  </si>
+  <si>
+    <t>Norias können nur in einem bestimmten Abstand zueinander errichtet werden.</t>
+  </si>
+  <si>
+    <t>Konsulate mit Gesandten in ihrem Radius produzieren Sultanssiegel, die später für den Lebensstil der Gesandten und weitere Zwecke verwendet werden können.</t>
+  </si>
+  <si>
+    <t>Wenn ein Marktstand mit ihren Waren beliefert wird, beginnt er, die Luxusbedürfnisse der Gesandten zu erfüllen, was Forschungspunkte generiert.</t>
+  </si>
+  <si>
+    <t>Dieses Monument ermöglicht es Ihnen, Pilgerfahrten durchzuführen, die Ihren Einfluss im Sultanat erhöhen.</t>
   </si>
 </sst>
 </file>
@@ -6911,12 +7058,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8138,7 +8286,7 @@
         <v>157</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -8161,7 +8309,7 @@
         <v>159</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -8175,16 +8323,16 @@
         <v>161</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="H56" t="s">
         <v>161</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -8198,16 +8346,16 @@
         <v>163</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="H57" t="s">
         <v>163</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -8230,7 +8378,7 @@
         <v>165</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -8244,16 +8392,16 @@
         <v>167</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="H59" t="s">
         <v>167</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -8276,7 +8424,7 @@
         <v>169</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -8299,7 +8447,7 @@
         <v>171</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -8322,7 +8470,7 @@
         <v>173</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -8345,7 +8493,7 @@
         <v>175</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -8368,7 +8516,7 @@
         <v>177</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -8391,7 +8539,7 @@
         <v>179</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -8414,7 +8562,7 @@
         <v>181</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -8437,7 +8585,7 @@
         <v>183</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -8460,7 +8608,7 @@
         <v>185</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -8483,7 +8631,7 @@
         <v>187</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -8506,7 +8654,7 @@
         <v>189</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -8529,7 +8677,7 @@
         <v>191</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -8552,7 +8700,7 @@
         <v>193</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
@@ -8575,7 +8723,7 @@
         <v>195</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -8598,7 +8746,7 @@
         <v>197</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -8621,7 +8769,7 @@
         <v>199</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
@@ -8644,7 +8792,7 @@
         <v>201</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
@@ -8667,7 +8815,7 @@
         <v>203</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -8690,7 +8838,7 @@
         <v>205</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -8713,7 +8861,7 @@
         <v>207</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
@@ -8736,7 +8884,7 @@
         <v>209</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
@@ -8759,7 +8907,7 @@
         <v>211</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -8782,7 +8930,7 @@
         <v>213</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -8805,7 +8953,7 @@
         <v>215</v>
       </c>
       <c r="N83" s="4" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -8828,7 +8976,7 @@
         <v>217</v>
       </c>
       <c r="N84" s="4" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
@@ -8851,7 +8999,7 @@
         <v>219</v>
       </c>
       <c r="N85" s="4" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -8874,7 +9022,7 @@
         <v>221</v>
       </c>
       <c r="N86" s="4" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -8897,7 +9045,7 @@
         <v>223</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
@@ -8920,7 +9068,7 @@
         <v>225</v>
       </c>
       <c r="N88" s="4" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -8943,7 +9091,7 @@
         <v>227</v>
       </c>
       <c r="N89" s="4" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -8966,7 +9114,7 @@
         <v>229</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -8989,7 +9137,7 @@
         <v>231</v>
       </c>
       <c r="N91" s="4" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
@@ -9012,7 +9160,7 @@
         <v>233</v>
       </c>
       <c r="N92" s="4" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
@@ -9035,7 +9183,7 @@
         <v>235</v>
       </c>
       <c r="N93" s="4" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -9058,7 +9206,7 @@
         <v>237</v>
       </c>
       <c r="N94" s="4" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -9081,7 +9229,7 @@
         <v>239</v>
       </c>
       <c r="N95" s="4" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -9104,7 +9252,7 @@
         <v>241</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -9127,7 +9275,7 @@
         <v>243</v>
       </c>
       <c r="N97" s="4" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -9150,7 +9298,7 @@
         <v>245</v>
       </c>
       <c r="N98" s="4" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -9173,7 +9321,7 @@
         <v>247</v>
       </c>
       <c r="N99" s="4" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
@@ -9196,7 +9344,7 @@
         <v>249</v>
       </c>
       <c r="N100" s="4" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
@@ -9219,7 +9367,7 @@
         <v>251</v>
       </c>
       <c r="N101" s="4" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -9242,7 +9390,7 @@
         <v>253</v>
       </c>
       <c r="N102" s="4" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
@@ -9265,7 +9413,7 @@
         <v>255</v>
       </c>
       <c r="N103" s="4" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -9288,7 +9436,7 @@
         <v>257</v>
       </c>
       <c r="N104" s="4" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
@@ -9311,7 +9459,7 @@
         <v>259</v>
       </c>
       <c r="N105" s="4" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
@@ -9334,7 +9482,7 @@
         <v>261</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
@@ -9357,7 +9505,7 @@
         <v>263</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
@@ -9380,7 +9528,7 @@
         <v>265</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
@@ -9403,7 +9551,7 @@
         <v>267</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
@@ -9426,7 +9574,7 @@
         <v>269</v>
       </c>
       <c r="N110" s="4" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -9449,7 +9597,7 @@
         <v>271</v>
       </c>
       <c r="N111" s="4" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
@@ -9472,7 +9620,7 @@
         <v>273</v>
       </c>
       <c r="N112" s="4" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
@@ -9495,7 +9643,7 @@
         <v>275</v>
       </c>
       <c r="N113" s="4" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -9518,7 +9666,7 @@
         <v>277</v>
       </c>
       <c r="N114" s="4" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
@@ -9541,7 +9689,7 @@
         <v>279</v>
       </c>
       <c r="N115" s="4" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
@@ -9564,7 +9712,7 @@
         <v>281</v>
       </c>
       <c r="N116" s="4" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
@@ -9587,7 +9735,7 @@
         <v>283</v>
       </c>
       <c r="N117" s="4" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
@@ -9610,7 +9758,7 @@
         <v>285</v>
       </c>
       <c r="N118" s="4" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
@@ -9633,7 +9781,7 @@
         <v>287</v>
       </c>
       <c r="N119" s="4" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
@@ -9656,7 +9804,7 @@
         <v>289</v>
       </c>
       <c r="N120" s="4" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
@@ -9679,7 +9827,7 @@
         <v>291</v>
       </c>
       <c r="N121" s="4" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
@@ -9702,7 +9850,7 @@
         <v>293</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
@@ -9725,7 +9873,7 @@
         <v>295</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -9748,7 +9896,7 @@
         <v>297</v>
       </c>
       <c r="N124" s="4" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
@@ -9771,7 +9919,7 @@
         <v>299</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
@@ -9794,7 +9942,7 @@
         <v>301</v>
       </c>
       <c r="N126" s="4" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
@@ -9817,7 +9965,7 @@
         <v>303</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
@@ -9840,7 +9988,7 @@
         <v>305</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
@@ -9863,7 +10011,7 @@
         <v>307</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
@@ -9886,7 +10034,7 @@
         <v>309</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
@@ -9909,7 +10057,7 @@
         <v>311</v>
       </c>
       <c r="N131" s="4" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -9923,16 +10071,16 @@
         <v>313</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="H132" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
@@ -9955,7 +10103,7 @@
         <v>315</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
@@ -9978,7 +10126,7 @@
         <v>318</v>
       </c>
       <c r="N134" s="4" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
@@ -10001,7 +10149,7 @@
         <v>320</v>
       </c>
       <c r="N135" s="4" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
@@ -10024,7 +10172,7 @@
         <v>322</v>
       </c>
       <c r="N136" s="4" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
@@ -10047,7 +10195,7 @@
         <v>325</v>
       </c>
       <c r="N137" s="4" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
@@ -10070,7 +10218,7 @@
         <v>327</v>
       </c>
       <c r="N138" s="4" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
@@ -10093,7 +10241,7 @@
         <v>330</v>
       </c>
       <c r="N139" s="4" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
@@ -10116,7 +10264,7 @@
         <v>332</v>
       </c>
       <c r="N140" s="4" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
@@ -10139,7 +10287,7 @@
         <v>334</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
@@ -10162,7 +10310,7 @@
         <v>336</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
@@ -10185,7 +10333,7 @@
         <v>338</v>
       </c>
       <c r="N143" s="4" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
@@ -10199,7 +10347,7 @@
         <v>340</v>
       </c>
       <c r="F144" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="H144" t="s">
         <v>341</v>
@@ -10340,7 +10488,7 @@
         <v>361</v>
       </c>
       <c r="F153" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="H153" t="s">
         <v>362</v>
@@ -10391,7 +10539,7 @@
         <v>365</v>
       </c>
       <c r="F156" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="H156" t="s">
         <v>373</v>
@@ -10408,7 +10556,7 @@
         <v>365</v>
       </c>
       <c r="F157" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="H157" t="s">
         <v>375</v>
@@ -10442,7 +10590,7 @@
         <v>365</v>
       </c>
       <c r="F159" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="H159" t="s">
         <v>381</v>
@@ -10541,7 +10689,7 @@
         <v>365</v>
       </c>
       <c r="F165" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="H165" t="s">
         <v>396</v>
@@ -10558,7 +10706,7 @@
         <v>398</v>
       </c>
       <c r="F166" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="H166" t="s">
         <v>399</v>
@@ -10634,7 +10782,7 @@
         <v>411</v>
       </c>
       <c r="F171" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="H171" t="s">
         <v>412</v>
@@ -10948,7 +11096,7 @@
         <v>462</v>
       </c>
       <c r="F193" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="H193" t="s">
         <v>463</v>
@@ -10965,7 +11113,7 @@
         <v>462</v>
       </c>
       <c r="F194" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="H194" t="s">
         <v>465</v>
@@ -10982,7 +11130,7 @@
         <v>462</v>
       </c>
       <c r="F195" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="H195" t="s">
         <v>467</v>
@@ -10999,7 +11147,7 @@
         <v>469</v>
       </c>
       <c r="F196" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="H196" t="s">
         <v>470</v>
@@ -11016,7 +11164,7 @@
         <v>472</v>
       </c>
       <c r="F197" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="H197" t="s">
         <v>473</v>
@@ -11075,7 +11223,7 @@
         <v>481</v>
       </c>
       <c r="F201" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="H201" t="s">
         <v>482</v>
@@ -11235,7 +11383,7 @@
         <v>510</v>
       </c>
       <c r="F212" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="H212" t="s">
         <v>511</v>
@@ -11926,7 +12074,7 @@
         <v>618</v>
       </c>
       <c r="F286" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="H286" t="s">
         <v>591</v>
@@ -12028,7 +12176,7 @@
         <v>630</v>
       </c>
       <c r="F292" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="H292" t="s">
         <v>601</v>
@@ -12062,7 +12210,7 @@
         <v>635</v>
       </c>
       <c r="F294" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="H294" t="s">
         <v>636</v>
@@ -12312,7 +12460,7 @@
         <v>654</v>
       </c>
       <c r="F314" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="H314" t="s">
         <v>673</v>
@@ -12351,7 +12499,7 @@
         <v>680</v>
       </c>
       <c r="F317" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="H317" t="s">
         <v>681</v>
@@ -12368,7 +12516,7 @@
         <v>683</v>
       </c>
       <c r="F318" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="H318" t="s">
         <v>684</v>
@@ -13077,7 +13225,7 @@
         <v>503</v>
       </c>
       <c r="F365" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="H365" t="s">
         <v>766</v>
@@ -13276,7 +13424,7 @@
         <v>799</v>
       </c>
       <c r="G379" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="H379" t="s">
         <v>800</v>
@@ -13310,7 +13458,7 @@
         <v>806</v>
       </c>
       <c r="G381" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="H381" t="s">
         <v>807</v>
@@ -13344,7 +13492,7 @@
         <v>813</v>
       </c>
       <c r="G383" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="H383" t="s">
         <v>814</v>
@@ -13378,7 +13526,7 @@
         <v>820</v>
       </c>
       <c r="G385" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="H385" t="s">
         <v>821</v>
@@ -13412,7 +13560,7 @@
         <v>827</v>
       </c>
       <c r="G387" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="H387" t="s">
         <v>828</v>
@@ -13446,7 +13594,7 @@
         <v>834</v>
       </c>
       <c r="G389" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="H389" t="s">
         <v>835</v>
@@ -13480,7 +13628,7 @@
         <v>841</v>
       </c>
       <c r="G391" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="H391" t="s">
         <v>842</v>
@@ -13514,7 +13662,7 @@
         <v>848</v>
       </c>
       <c r="G393" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="H393" t="s">
         <v>849</v>
@@ -13548,7 +13696,7 @@
         <v>855</v>
       </c>
       <c r="G395" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="H395" t="s">
         <v>856</v>
@@ -13616,7 +13764,7 @@
         <v>870</v>
       </c>
       <c r="G399" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="H399" t="s">
         <v>871</v>
@@ -13752,7 +13900,7 @@
         <v>901</v>
       </c>
       <c r="G407" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="H407" t="s">
         <v>902</v>
@@ -13786,7 +13934,7 @@
         <v>908</v>
       </c>
       <c r="G409" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="H409" t="s">
         <v>909</v>
@@ -13888,7 +14036,7 @@
         <v>931</v>
       </c>
       <c r="G415" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="H415" t="s">
         <v>932</v>
@@ -13922,7 +14070,7 @@
         <v>938</v>
       </c>
       <c r="G417" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="H417" t="s">
         <v>939</v>
@@ -13956,7 +14104,7 @@
         <v>945</v>
       </c>
       <c r="G419" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="H419" t="s">
         <v>946</v>
@@ -13990,7 +14138,7 @@
         <v>952</v>
       </c>
       <c r="G421" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="H421" t="s">
         <v>953</v>
@@ -14024,7 +14172,7 @@
         <v>959</v>
       </c>
       <c r="G423" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="H423" t="s">
         <v>960</v>
@@ -14126,7 +14274,7 @@
         <v>982</v>
       </c>
       <c r="G429" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="H429" t="s">
         <v>983</v>
@@ -14160,7 +14308,7 @@
         <v>989</v>
       </c>
       <c r="G431" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="H431" t="s">
         <v>990</v>
@@ -14296,7 +14444,7 @@
         <v>1020</v>
       </c>
       <c r="G439" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="H439" t="s">
         <v>1021</v>
@@ -14330,7 +14478,7 @@
         <v>1027</v>
       </c>
       <c r="G441" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="H441" t="s">
         <v>1028</v>
@@ -14398,7 +14546,7 @@
         <v>1042</v>
       </c>
       <c r="G445" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="H445" t="s">
         <v>1043</v>
@@ -14432,7 +14580,7 @@
         <v>1049</v>
       </c>
       <c r="G447" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="H447" t="s">
         <v>1050</v>
@@ -14466,7 +14614,7 @@
         <v>1056</v>
       </c>
       <c r="G449" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="H449" t="s">
         <v>1057</v>
@@ -14500,7 +14648,7 @@
         <v>1063</v>
       </c>
       <c r="G451" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="H451" t="s">
         <v>1064</v>
@@ -14534,7 +14682,7 @@
         <v>1070</v>
       </c>
       <c r="G453" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="H453" t="s">
         <v>1071</v>
@@ -14568,7 +14716,7 @@
         <v>1077</v>
       </c>
       <c r="G455" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="H455" t="s">
         <v>1078</v>
@@ -14613,7 +14761,7 @@
         <v>1086</v>
       </c>
       <c r="G458" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="H458" t="s">
         <v>1087</v>
@@ -14681,7 +14829,7 @@
         <v>1101</v>
       </c>
       <c r="G462" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="H462" t="s">
         <v>1102</v>
@@ -14715,7 +14863,7 @@
         <v>1108</v>
       </c>
       <c r="G464" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="H464" t="s">
         <v>1109</v>
@@ -14749,7 +14897,7 @@
         <v>1115</v>
       </c>
       <c r="G466" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="H466" t="s">
         <v>1116</v>
@@ -14783,7 +14931,7 @@
         <v>1122</v>
       </c>
       <c r="G468" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="H468" t="s">
         <v>1123</v>
@@ -14817,7 +14965,7 @@
         <v>1129</v>
       </c>
       <c r="G470" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="H470" t="s">
         <v>1130</v>
@@ -14851,7 +14999,7 @@
         <v>1136</v>
       </c>
       <c r="G472" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="H472" t="s">
         <v>1137</v>
@@ -14953,7 +15101,7 @@
         <v>1159</v>
       </c>
       <c r="G478" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="H478" t="s">
         <v>1160</v>
@@ -14987,7 +15135,7 @@
         <v>1166</v>
       </c>
       <c r="G480" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="H480" t="s">
         <v>1167</v>
@@ -15089,7 +15237,7 @@
         <v>1189</v>
       </c>
       <c r="G486" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="H486" t="s">
         <v>1190</v>
@@ -15123,7 +15271,7 @@
         <v>1196</v>
       </c>
       <c r="G488" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="H488" t="s">
         <v>1197</v>
@@ -15157,7 +15305,7 @@
         <v>1203</v>
       </c>
       <c r="G490" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="H490" t="s">
         <v>1204</v>
@@ -15191,7 +15339,7 @@
         <v>1210</v>
       </c>
       <c r="G492" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="H492" t="s">
         <v>1211</v>
@@ -15327,7 +15475,7 @@
         <v>1241</v>
       </c>
       <c r="G500" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="H500" t="s">
         <v>1242</v>
@@ -15361,7 +15509,7 @@
         <v>1248</v>
       </c>
       <c r="G502" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="H502" t="s">
         <v>1249</v>
@@ -15395,7 +15543,7 @@
         <v>1255</v>
       </c>
       <c r="G504" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="H504" t="s">
         <v>1256</v>
@@ -15429,7 +15577,7 @@
         <v>1262</v>
       </c>
       <c r="G506" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="H506" t="s">
         <v>1263</v>
@@ -15497,7 +15645,7 @@
         <v>1277</v>
       </c>
       <c r="G510" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="H510" t="s">
         <v>1278</v>
@@ -15531,7 +15679,7 @@
         <v>1284</v>
       </c>
       <c r="G512" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="H512" t="s">
         <v>1285</v>
@@ -15599,7 +15747,7 @@
         <v>1299</v>
       </c>
       <c r="G516" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="H516" t="s">
         <v>1300</v>
@@ -15633,7 +15781,7 @@
         <v>1306</v>
       </c>
       <c r="G518" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="H518" t="s">
         <v>1307</v>
@@ -15667,7 +15815,7 @@
         <v>1313</v>
       </c>
       <c r="G520" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="H520" t="s">
         <v>1314</v>
@@ -15769,7 +15917,7 @@
         <v>1336</v>
       </c>
       <c r="G526" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="H526" t="s">
         <v>1337</v>
@@ -15803,7 +15951,7 @@
         <v>1343</v>
       </c>
       <c r="G528" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="H528" t="s">
         <v>1344</v>
@@ -15837,7 +15985,7 @@
         <v>1350</v>
       </c>
       <c r="G530" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="H530" t="s">
         <v>1351</v>
@@ -15871,7 +16019,7 @@
         <v>1357</v>
       </c>
       <c r="G532" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="H532" t="s">
         <v>1358</v>
@@ -15905,7 +16053,7 @@
         <v>1364</v>
       </c>
       <c r="G534" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="H534" t="s">
         <v>1365</v>
@@ -15939,7 +16087,7 @@
         <v>1371</v>
       </c>
       <c r="G536" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="H536" t="s">
         <v>1372</v>
@@ -15973,7 +16121,7 @@
         <v>1378</v>
       </c>
       <c r="G538" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="H538" t="s">
         <v>1379</v>
@@ -16007,7 +16155,7 @@
         <v>1385</v>
       </c>
       <c r="G540" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="H540" t="s">
         <v>1386</v>
@@ -16075,7 +16223,7 @@
         <v>1400</v>
       </c>
       <c r="G544" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="H544" t="s">
         <v>1401</v>
@@ -16143,7 +16291,7 @@
         <v>1415</v>
       </c>
       <c r="G548" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="H548" t="s">
         <v>1416</v>
@@ -16177,7 +16325,7 @@
         <v>1422</v>
       </c>
       <c r="G550" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="H550" t="s">
         <v>1423</v>
@@ -16211,7 +16359,7 @@
         <v>1429</v>
       </c>
       <c r="G552" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="H552" t="s">
         <v>1430</v>
@@ -16561,7 +16709,7 @@
         <v>1468</v>
       </c>
       <c r="F577" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="H577" t="s">
         <v>1469</v>
@@ -16578,7 +16726,7 @@
         <v>1468</v>
       </c>
       <c r="F578" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="H578" t="s">
         <v>1471</v>
@@ -16595,7 +16743,7 @@
         <v>1473</v>
       </c>
       <c r="F579" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="H579" t="s">
         <v>1474</v>
@@ -16612,7 +16760,7 @@
         <v>1473</v>
       </c>
       <c r="F580" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="H580" t="s">
         <v>1476</v>
@@ -16629,7 +16777,7 @@
         <v>462</v>
       </c>
       <c r="F581" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="H581" t="s">
         <v>1478</v>
@@ -16646,7 +16794,7 @@
         <v>1480</v>
       </c>
       <c r="F582" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="H582" t="s">
         <v>1481</v>
@@ -16691,7 +16839,7 @@
         <v>1487</v>
       </c>
       <c r="F585" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="H585" t="s">
         <v>1487</v>
@@ -16708,7 +16856,7 @@
         <v>1489</v>
       </c>
       <c r="F586" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="H586" t="s">
         <v>1490</v>
@@ -16725,7 +16873,7 @@
         <v>1492</v>
       </c>
       <c r="F587" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="H587" t="s">
         <v>1493</v>
@@ -16742,7 +16890,7 @@
         <v>1495</v>
       </c>
       <c r="F588" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="H588" t="s">
         <v>1495</v>
@@ -16759,7 +16907,7 @@
         <v>462</v>
       </c>
       <c r="F589" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="H589" t="s">
         <v>1497</v>
@@ -19208,7 +19356,7 @@
         <v>503</v>
       </c>
       <c r="F786" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="H786" t="s">
         <v>1839</v>
@@ -19222,10 +19370,10 @@
         <v>22</v>
       </c>
       <c r="C787" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="F787" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="H787" t="s">
         <v>1841</v>
@@ -19239,10 +19387,10 @@
         <v>22</v>
       </c>
       <c r="C788" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="F788" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="H788" t="s">
         <v>1843</v>
@@ -19256,10 +19404,10 @@
         <v>22</v>
       </c>
       <c r="C789" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="F789" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="H789" t="s">
         <v>1845</v>
@@ -19315,127 +19463,154 @@
         <v>1856</v>
       </c>
       <c r="C793" t="s">
-        <v>1857</v>
+        <v>2283</v>
+      </c>
+      <c r="F793" t="s">
+        <v>2283</v>
       </c>
       <c r="H793" t="s">
-        <v>27</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B794" t="s">
         <v>1858</v>
       </c>
-      <c r="B794" t="s">
-        <v>1859</v>
-      </c>
       <c r="C794" t="s">
-        <v>27</v>
+        <v>2284</v>
+      </c>
+      <c r="F794" t="s">
+        <v>2284</v>
       </c>
       <c r="H794" t="s">
-        <v>27</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="B795" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C795" t="s">
-        <v>27</v>
+        <v>2285</v>
+      </c>
+      <c r="F795" t="s">
+        <v>2285</v>
       </c>
       <c r="H795" t="s">
-        <v>27</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B796" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C796" t="s">
-        <v>27</v>
+        <v>2291</v>
+      </c>
+      <c r="F796" t="s">
+        <v>2291</v>
       </c>
       <c r="H796" t="s">
-        <v>27</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="B797" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C797" t="s">
-        <v>27</v>
+        <v>2287</v>
+      </c>
+      <c r="F797" t="s">
+        <v>2287</v>
       </c>
       <c r="H797" t="s">
-        <v>27</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B798" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C798" t="s">
-        <v>27</v>
+        <v>2288</v>
+      </c>
+      <c r="F798" t="s">
+        <v>2288</v>
       </c>
       <c r="H798" t="s">
-        <v>27</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="B799" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C799" t="s">
-        <v>27</v>
+        <v>2286</v>
+      </c>
+      <c r="F799" t="s">
+        <v>2286</v>
       </c>
       <c r="H799" t="s">
-        <v>27</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="B800" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C800" t="s">
-        <v>27</v>
+        <v>2289</v>
+      </c>
+      <c r="F800" t="s">
+        <v>2289</v>
       </c>
       <c r="H800" t="s">
-        <v>27</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="B801" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C801" t="s">
-        <v>27</v>
+        <v>2290</v>
+      </c>
+      <c r="F801" t="s">
+        <v>2290</v>
       </c>
       <c r="H801" t="s">
-        <v>27</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H802" t="s">
         <v>27</v>
@@ -19443,7 +19618,7 @@
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H803" t="s">
         <v>27</v>
@@ -19451,13 +19626,13 @@
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B804" t="s">
         <v>1869</v>
       </c>
-      <c r="B804" t="s">
+      <c r="C804" t="s">
         <v>1870</v>
-      </c>
-      <c r="C804" t="s">
-        <v>1871</v>
       </c>
       <c r="H804" t="s">
         <v>27</v>
@@ -19465,13 +19640,13 @@
     </row>
     <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B805" t="s">
+        <v>22</v>
+      </c>
+      <c r="C805" t="s">
         <v>1872</v>
-      </c>
-      <c r="B805" t="s">
-        <v>22</v>
-      </c>
-      <c r="C805" t="s">
-        <v>1873</v>
       </c>
       <c r="H805" t="s">
         <v>27</v>
@@ -19479,13 +19654,13 @@
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B806" t="s">
+        <v>22</v>
+      </c>
+      <c r="C806" t="s">
         <v>1874</v>
-      </c>
-      <c r="B806" t="s">
-        <v>22</v>
-      </c>
-      <c r="C806" t="s">
-        <v>1875</v>
       </c>
       <c r="H806" t="s">
         <v>27</v>
@@ -19493,13 +19668,13 @@
     </row>
     <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B807" t="s">
         <v>126</v>
       </c>
       <c r="C807" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H807" t="s">
         <v>27</v>
@@ -19507,13 +19682,13 @@
     </row>
     <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B808" t="s">
         <v>126</v>
       </c>
       <c r="C808" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H808" t="s">
         <v>27</v>
@@ -19521,13 +19696,13 @@
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="B809" t="s">
         <v>126</v>
       </c>
       <c r="C809" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H809" t="s">
         <v>27</v>
@@ -19535,13 +19710,13 @@
     </row>
     <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="B810" t="s">
         <v>126</v>
       </c>
       <c r="C810" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H810" t="s">
         <v>27</v>
@@ -19549,13 +19724,13 @@
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="B811" t="s">
         <v>126</v>
       </c>
       <c r="C811" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H811" t="s">
         <v>27</v>
@@ -19563,13 +19738,13 @@
     </row>
     <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="B812" t="s">
         <v>126</v>
       </c>
       <c r="C812" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H812" t="s">
         <v>27</v>
@@ -19577,13 +19752,13 @@
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B813" t="s">
         <v>126</v>
       </c>
       <c r="C813" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H813" t="s">
         <v>27</v>
@@ -19591,13 +19766,13 @@
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B814" t="s">
         <v>126</v>
       </c>
       <c r="C814" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H814" t="s">
         <v>27</v>
@@ -19605,13 +19780,13 @@
     </row>
     <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B815" t="s">
         <v>126</v>
       </c>
       <c r="C815" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H815" t="s">
         <v>27</v>
@@ -19619,13 +19794,13 @@
     </row>
     <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B816" t="s">
         <v>126</v>
       </c>
       <c r="C816" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H816" t="s">
         <v>27</v>
@@ -19633,13 +19808,13 @@
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B817" t="s">
         <v>126</v>
       </c>
       <c r="C817" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H817" t="s">
         <v>27</v>
@@ -19647,13 +19822,13 @@
     </row>
     <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B818" t="s">
         <v>126</v>
       </c>
       <c r="C818" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H818" t="s">
         <v>27</v>
@@ -19661,13 +19836,13 @@
     </row>
     <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B819" t="s">
         <v>126</v>
       </c>
       <c r="C819" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H819" t="s">
         <v>27</v>
@@ -19675,13 +19850,13 @@
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B820" t="s">
         <v>126</v>
       </c>
       <c r="C820" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H820" t="s">
         <v>27</v>
@@ -19689,135 +19864,279 @@
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>1904</v>
+        <v>1903</v>
+      </c>
+      <c r="B821" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C821" s="5" t="s">
+        <v>2267</v>
+      </c>
+      <c r="F821" s="5" t="s">
+        <v>2267</v>
       </c>
       <c r="H821" t="s">
-        <v>27</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>1905</v>
+        <v>1904</v>
+      </c>
+      <c r="B822" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C822" s="5" t="s">
+        <v>2268</v>
+      </c>
+      <c r="F822" s="5" t="s">
+        <v>2268</v>
       </c>
       <c r="H822" t="s">
-        <v>27</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>1906</v>
+        <v>1905</v>
+      </c>
+      <c r="B823" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C823" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F823" s="5" t="s">
+        <v>2269</v>
       </c>
       <c r="H823" t="s">
-        <v>27</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>1907</v>
+        <v>1906</v>
+      </c>
+      <c r="B824" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C824" s="5" t="s">
+        <v>2270</v>
+      </c>
+      <c r="F824" s="5" t="s">
+        <v>2270</v>
       </c>
       <c r="H824" t="s">
-        <v>27</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>1908</v>
+        <v>1907</v>
+      </c>
+      <c r="B825" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C825" s="5" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F825" s="5" t="s">
+        <v>2271</v>
       </c>
       <c r="H825" t="s">
-        <v>27</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>1909</v>
+        <v>1908</v>
+      </c>
+      <c r="B826" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C826" s="5" t="s">
+        <v>2272</v>
+      </c>
+      <c r="F826" s="5" t="s">
+        <v>2272</v>
       </c>
       <c r="H826" t="s">
-        <v>27</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>1910</v>
+        <v>1909</v>
+      </c>
+      <c r="B827" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C827" s="5" t="s">
+        <v>2273</v>
+      </c>
+      <c r="F827" s="5" t="s">
+        <v>2273</v>
       </c>
       <c r="H827" t="s">
-        <v>27</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>1911</v>
+        <v>1910</v>
+      </c>
+      <c r="B828" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C828" s="5" t="s">
+        <v>2274</v>
+      </c>
+      <c r="F828" s="5" t="s">
+        <v>2274</v>
       </c>
       <c r="H828" t="s">
-        <v>27</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>1912</v>
+        <v>1911</v>
+      </c>
+      <c r="B829" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C829" s="5" t="s">
+        <v>2275</v>
+      </c>
+      <c r="F829" s="5" t="s">
+        <v>2275</v>
       </c>
       <c r="H829" t="s">
-        <v>27</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>1913</v>
+        <v>1912</v>
+      </c>
+      <c r="B830" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C830" s="5" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F830" s="5" t="s">
+        <v>2276</v>
       </c>
       <c r="H830" t="s">
-        <v>27</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>1914</v>
+        <v>1913</v>
+      </c>
+      <c r="B831" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C831" s="5" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F831" s="5" t="s">
+        <v>2277</v>
       </c>
       <c r="H831" t="s">
-        <v>27</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>1915</v>
+        <v>1914</v>
+      </c>
+      <c r="B832" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C832" s="5" t="s">
+        <v>2278</v>
+      </c>
+      <c r="F832" s="5" t="s">
+        <v>2278</v>
       </c>
       <c r="H832" t="s">
-        <v>27</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>1916</v>
+        <v>1915</v>
+      </c>
+      <c r="B833" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C833" s="5" t="s">
+        <v>2279</v>
+      </c>
+      <c r="F833" s="5" t="s">
+        <v>2279</v>
       </c>
       <c r="H833" t="s">
-        <v>27</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>1917</v>
+        <v>1916</v>
+      </c>
+      <c r="B834" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C834" s="5" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F834" s="5" t="s">
+        <v>2280</v>
       </c>
       <c r="H834" t="s">
-        <v>27</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>1918</v>
+        <v>1917</v>
+      </c>
+      <c r="B835" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C835" s="5" t="s">
+        <v>2281</v>
+      </c>
+      <c r="F835" s="5" t="s">
+        <v>2281</v>
       </c>
       <c r="H835" t="s">
-        <v>27</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>1919</v>
+        <v>1918</v>
+      </c>
+      <c r="B836" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C836" s="5" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F836" s="5" t="s">
+        <v>2282</v>
       </c>
       <c r="H836" t="s">
-        <v>27</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H837" t="s">
         <v>27</v>
@@ -19825,7 +20144,7 @@
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H838" t="s">
         <v>27</v>
@@ -19833,7 +20152,7 @@
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H839" t="s">
         <v>27</v>
@@ -19841,7 +20160,7 @@
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H840" t="s">
         <v>27</v>
@@ -19849,7 +20168,7 @@
     </row>
     <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H841" t="s">
         <v>27</v>
@@ -19857,7 +20176,7 @@
     </row>
     <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H842" t="s">
         <v>27</v>
@@ -19865,7 +20184,7 @@
     </row>
     <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H843" t="s">
         <v>27</v>
@@ -19873,7 +20192,7 @@
     </row>
     <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H844" t="s">
         <v>27</v>
@@ -19881,7 +20200,7 @@
     </row>
     <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H845" t="s">
         <v>27</v>
@@ -19889,7 +20208,7 @@
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H846" t="s">
         <v>27</v>
@@ -19897,7 +20216,7 @@
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H847" t="s">
         <v>27</v>
@@ -19905,7 +20224,7 @@
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H848" t="s">
         <v>27</v>
@@ -19913,7 +20232,7 @@
     </row>
     <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H849" t="s">
         <v>27</v>
@@ -19921,7 +20240,7 @@
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H850" t="s">
         <v>27</v>
@@ -19929,7 +20248,7 @@
     </row>
     <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H851" t="s">
         <v>27</v>
@@ -19937,7 +20256,7 @@
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H852" t="s">
         <v>27</v>
@@ -19945,7 +20264,7 @@
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H853" t="s">
         <v>27</v>
@@ -19953,7 +20272,7 @@
     </row>
     <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H854" t="s">
         <v>27</v>
@@ -19961,7 +20280,7 @@
     </row>
     <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H855" t="s">
         <v>27</v>
@@ -19969,7 +20288,7 @@
     </row>
     <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H856" t="s">
         <v>27</v>
@@ -19977,7 +20296,7 @@
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H857" t="s">
         <v>27</v>
@@ -19985,7 +20304,7 @@
     </row>
     <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H858" t="s">
         <v>27</v>
@@ -19993,7 +20312,7 @@
     </row>
     <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H859" t="s">
         <v>27</v>
@@ -20001,7 +20320,7 @@
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H860" t="s">
         <v>27</v>
@@ -20009,7 +20328,7 @@
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H861" t="s">
         <v>27</v>
@@ -20017,7 +20336,7 @@
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H862" t="s">
         <v>27</v>
@@ -20025,7 +20344,7 @@
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H863" t="s">
         <v>27</v>
@@ -20033,7 +20352,7 @@
     </row>
     <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H864" t="s">
         <v>27</v>
@@ -20041,7 +20360,7 @@
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H865" t="s">
         <v>27</v>
@@ -20049,7 +20368,7 @@
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H866" t="s">
         <v>27</v>
@@ -20057,7 +20376,7 @@
     </row>
     <row r="867" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H867" t="s">
         <v>27</v>
@@ -20065,7 +20384,7 @@
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H868" t="s">
         <v>27</v>
@@ -20073,7 +20392,7 @@
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H869" t="s">
         <v>27</v>
@@ -20081,7 +20400,7 @@
     </row>
     <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H870" t="s">
         <v>27</v>
@@ -20089,7 +20408,7 @@
     </row>
     <row r="871" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H871" t="s">
         <v>27</v>
@@ -20097,7 +20416,7 @@
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H872" t="s">
         <v>27</v>
@@ -20105,7 +20424,7 @@
     </row>
     <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H873" t="s">
         <v>27</v>
@@ -20113,7 +20432,7 @@
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H874" t="s">
         <v>27</v>
@@ -20121,7 +20440,7 @@
     </row>
     <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H875" t="s">
         <v>27</v>
@@ -20129,7 +20448,7 @@
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H876" t="s">
         <v>27</v>
@@ -20137,7 +20456,7 @@
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H877" t="s">
         <v>27</v>
@@ -20145,7 +20464,7 @@
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H878" t="s">
         <v>27</v>
@@ -20153,7 +20472,7 @@
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H879" t="s">
         <v>27</v>
@@ -20161,7 +20480,7 @@
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H880" t="s">
         <v>27</v>
@@ -20169,7 +20488,7 @@
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H881" t="s">
         <v>27</v>
@@ -20177,7 +20496,7 @@
     </row>
     <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H882" t="s">
         <v>27</v>
@@ -20185,7 +20504,7 @@
     </row>
     <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H883" t="s">
         <v>27</v>
@@ -20193,7 +20512,7 @@
     </row>
     <row r="884" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H884" t="s">
         <v>27</v>
@@ -20201,7 +20520,7 @@
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H885" t="s">
         <v>27</v>
@@ -20209,7 +20528,7 @@
     </row>
     <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H886" t="s">
         <v>27</v>
@@ -20217,7 +20536,7 @@
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H887" t="s">
         <v>27</v>
@@ -20225,7 +20544,7 @@
     </row>
     <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H888" t="s">
         <v>27</v>
@@ -20233,7 +20552,7 @@
     </row>
     <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H889" t="s">
         <v>27</v>
@@ -20241,7 +20560,7 @@
     </row>
     <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H890" t="s">
         <v>27</v>
@@ -20249,7 +20568,7 @@
     </row>
     <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H891" t="s">
         <v>27</v>
@@ -20257,7 +20576,7 @@
     </row>
     <row r="892" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H892" t="s">
         <v>27</v>
@@ -20265,7 +20584,7 @@
     </row>
     <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H893" t="s">
         <v>27</v>
@@ -20273,7 +20592,7 @@
     </row>
     <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H894" t="s">
         <v>27</v>
@@ -20281,7 +20600,7 @@
     </row>
     <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H895" t="s">
         <v>27</v>
@@ -20289,7 +20608,7 @@
     </row>
     <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H896" t="s">
         <v>27</v>
@@ -20297,7 +20616,7 @@
     </row>
     <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H897" t="s">
         <v>27</v>
@@ -20305,7 +20624,7 @@
     </row>
     <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H898" t="s">
         <v>27</v>
@@ -20313,7 +20632,7 @@
     </row>
     <row r="899" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H899" t="s">
         <v>27</v>
@@ -20321,7 +20640,7 @@
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H900" t="s">
         <v>27</v>
@@ -20329,7 +20648,7 @@
     </row>
     <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H901" t="s">
         <v>27</v>
@@ -20337,7 +20656,7 @@
     </row>
     <row r="902" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H902" t="s">
         <v>27</v>
@@ -20345,7 +20664,7 @@
     </row>
     <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H903" t="s">
         <v>27</v>
@@ -20353,7 +20672,7 @@
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H904" t="s">
         <v>27</v>
@@ -20361,7 +20680,7 @@
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H905" t="s">
         <v>27</v>
@@ -20369,7 +20688,7 @@
     </row>
     <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H906" t="s">
         <v>27</v>
@@ -20377,7 +20696,7 @@
     </row>
     <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H907" t="s">
         <v>27</v>
@@ -20385,7 +20704,7 @@
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H908" t="s">
         <v>27</v>
@@ -20393,7 +20712,7 @@
     </row>
     <row r="909" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H909" t="s">
         <v>27</v>
@@ -20401,7 +20720,7 @@
     </row>
     <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H910" t="s">
         <v>27</v>
@@ -20409,7 +20728,7 @@
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H911" t="s">
         <v>27</v>
@@ -20417,7 +20736,7 @@
     </row>
     <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H912" t="s">
         <v>27</v>
@@ -20425,7 +20744,7 @@
     </row>
     <row r="913" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H913" t="s">
         <v>27</v>
@@ -20433,7 +20752,7 @@
     </row>
     <row r="914" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H914" t="s">
         <v>27</v>
@@ -20441,7 +20760,7 @@
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H915" t="s">
         <v>27</v>
@@ -20449,7 +20768,7 @@
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H916" t="s">
         <v>27</v>
@@ -20457,7 +20776,7 @@
     </row>
     <row r="917" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H917" t="s">
         <v>27</v>
@@ -20465,7 +20784,7 @@
     </row>
     <row r="918" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H918" t="s">
         <v>27</v>
@@ -20473,7 +20792,7 @@
     </row>
     <row r="919" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H919" t="s">
         <v>27</v>
@@ -20481,7 +20800,7 @@
     </row>
     <row r="920" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H920" t="s">
         <v>27</v>
@@ -20489,7 +20808,7 @@
     </row>
     <row r="921" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H921" t="s">
         <v>27</v>
@@ -20497,7 +20816,7 @@
     </row>
     <row r="922" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H922" t="s">
         <v>27</v>
@@ -20505,7 +20824,7 @@
     </row>
     <row r="923" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H923" t="s">
         <v>27</v>
@@ -20513,7 +20832,7 @@
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H924" t="s">
         <v>27</v>
@@ -20521,7 +20840,7 @@
     </row>
     <row r="925" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H925" t="s">
         <v>27</v>
@@ -20529,7 +20848,7 @@
     </row>
     <row r="926" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H926" t="s">
         <v>27</v>
@@ -20537,7 +20856,7 @@
     </row>
     <row r="927" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H927" t="s">
         <v>27</v>
@@ -20545,7 +20864,7 @@
     </row>
     <row r="928" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H928" t="s">
         <v>27</v>
@@ -20553,7 +20872,7 @@
     </row>
     <row r="929" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H929" t="s">
         <v>27</v>
@@ -20561,7 +20880,7 @@
     </row>
     <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H930" t="s">
         <v>27</v>
@@ -20569,7 +20888,7 @@
     </row>
     <row r="931" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H931" t="s">
         <v>27</v>
@@ -20577,7 +20896,7 @@
     </row>
     <row r="932" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H932" t="s">
         <v>27</v>
@@ -20585,7 +20904,7 @@
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H933" t="s">
         <v>27</v>
@@ -20593,7 +20912,7 @@
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H934" t="s">
         <v>27</v>
@@ -20601,7 +20920,7 @@
     </row>
     <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H935" t="s">
         <v>27</v>
@@ -20609,7 +20928,7 @@
     </row>
     <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H936" t="s">
         <v>27</v>
@@ -20617,7 +20936,7 @@
     </row>
     <row r="937" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H937" t="s">
         <v>27</v>
@@ -20625,7 +20944,7 @@
     </row>
     <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H938" t="s">
         <v>27</v>
@@ -20633,7 +20952,7 @@
     </row>
     <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H939" t="s">
         <v>27</v>
@@ -20641,7 +20960,7 @@
     </row>
     <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H940" t="s">
         <v>27</v>
@@ -20649,7 +20968,7 @@
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H941" t="s">
         <v>27</v>
@@ -20657,7 +20976,7 @@
     </row>
     <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H942" t="s">
         <v>27</v>
@@ -20665,7 +20984,7 @@
     </row>
     <row r="943" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H943" t="s">
         <v>27</v>
@@ -20673,7 +20992,7 @@
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="H944" t="s">
         <v>27</v>
@@ -20681,7 +21000,7 @@
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="H945" t="s">
         <v>27</v>
@@ -20689,7 +21008,7 @@
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="H946" t="s">
         <v>27</v>
@@ -20697,7 +21016,7 @@
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="H947" t="s">
         <v>27</v>
@@ -20705,7 +21024,7 @@
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="H948" t="s">
         <v>27</v>
@@ -20713,7 +21032,7 @@
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="H949" t="s">
         <v>27</v>
@@ -20721,7 +21040,7 @@
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="H950" t="s">
         <v>27</v>
@@ -20729,7 +21048,7 @@
     </row>
     <row r="951" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="H951" t="s">
         <v>27</v>
@@ -20737,7 +21056,7 @@
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="H952" t="s">
         <v>27</v>
@@ -20745,7 +21064,7 @@
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="H953" t="s">
         <v>27</v>
@@ -20753,7 +21072,7 @@
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="H954" t="s">
         <v>27</v>
@@ -20761,7 +21080,7 @@
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="H955" t="s">
         <v>27</v>
@@ -20769,7 +21088,7 @@
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="H956" t="s">
         <v>27</v>
@@ -20777,7 +21096,7 @@
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="H957" t="s">
         <v>27</v>
@@ -20785,7 +21104,7 @@
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="H958" t="s">
         <v>27</v>
@@ -20793,7 +21112,7 @@
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="H959" t="s">
         <v>27</v>
@@ -20801,7 +21120,7 @@
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="H960" t="s">
         <v>27</v>
@@ -20809,7 +21128,7 @@
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="H961" t="s">
         <v>27</v>
@@ -20817,7 +21136,7 @@
     </row>
     <row r="962" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="H962" t="s">
         <v>27</v>
@@ -20825,7 +21144,7 @@
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="H963" t="s">
         <v>27</v>
@@ -20833,7 +21152,7 @@
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="H964" t="s">
         <v>27</v>
@@ -20841,7 +21160,7 @@
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="H965" t="s">
         <v>27</v>
@@ -20849,7 +21168,7 @@
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="H966" t="s">
         <v>27</v>
@@ -20857,7 +21176,7 @@
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="H967" t="s">
         <v>27</v>
@@ -20865,7 +21184,7 @@
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="H968" t="s">
         <v>27</v>
@@ -20873,7 +21192,7 @@
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="H969" t="s">
         <v>27</v>
@@ -20881,7 +21200,7 @@
     </row>
     <row r="970" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="H970" t="s">
         <v>27</v>
@@ -20889,7 +21208,7 @@
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="H971" t="s">
         <v>27</v>
@@ -20897,7 +21216,7 @@
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="H972" t="s">
         <v>27</v>
@@ -20905,7 +21224,7 @@
     </row>
     <row r="973" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="H973" t="s">
         <v>27</v>
@@ -20913,7 +21232,7 @@
     </row>
     <row r="974" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="H974" t="s">
         <v>27</v>
@@ -20921,7 +21240,7 @@
     </row>
     <row r="975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="H975" t="s">
         <v>27</v>
@@ -20929,7 +21248,7 @@
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="H976" t="s">
         <v>27</v>
@@ -20937,7 +21256,7 @@
     </row>
     <row r="977" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="H977" t="s">
         <v>27</v>
@@ -20945,7 +21264,7 @@
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="H978" t="s">
         <v>27</v>
@@ -20953,7 +21272,7 @@
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="H979" t="s">
         <v>27</v>
@@ -20961,7 +21280,7 @@
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="H980" t="s">
         <v>27</v>
@@ -20969,7 +21288,7 @@
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="H981" t="s">
         <v>27</v>
@@ -20977,7 +21296,7 @@
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="H982" t="s">
         <v>27</v>
@@ -20985,7 +21304,7 @@
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="H983" t="s">
         <v>27</v>
@@ -20993,7 +21312,7 @@
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="H984" t="s">
         <v>27</v>
@@ -21001,7 +21320,7 @@
     </row>
     <row r="985" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="H985" t="s">
         <v>27</v>
@@ -21009,7 +21328,7 @@
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="H986" t="s">
         <v>27</v>
@@ -21017,7 +21336,7 @@
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="H987" t="s">
         <v>27</v>
@@ -21025,7 +21344,7 @@
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="H988" t="s">
         <v>27</v>
@@ -21033,7 +21352,7 @@
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="H989" t="s">
         <v>27</v>
@@ -21041,7 +21360,7 @@
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="H990" t="s">
         <v>27</v>
@@ -21049,7 +21368,7 @@
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="H991" t="s">
         <v>27</v>
@@ -21057,7 +21376,7 @@
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="H992" t="s">
         <v>27</v>

--- a/data/config/gui/_Localizations.xlsx
+++ b/data/config/gui/_Localizations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\Anno 1800\mods\[Addon] Return to the Orient\data\config\gui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471CE549-B700-4896-9980-983CB1C27B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D41D238-8552-40B5-9ECA-6098061EF790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6360" yWindow="3555" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Localization" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4015" uniqueCount="2317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4007" uniqueCount="2318">
   <si>
     <t>GUID</t>
   </si>
@@ -6988,6 +6988,9 @@
   </si>
   <si>
     <t>Dieses Monument ermöglicht es Ihnen, Pilgerfahrten durchzuführen, die Ihren Einfluss im Sultanat erhöhen.</t>
+  </si>
+  <si>
+    <t>Oriental Workshop: Hookahs</t>
   </si>
 </sst>
 </file>
@@ -7367,6 +7370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P992"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7427,7 +7431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7477,7 +7481,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -7494,7 +7498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -7511,7 +7515,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -7528,7 +7532,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -7559,7 +7563,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -7578,39 +7582,39 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>374</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>372</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>365</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>2081</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>466</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>461</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>462</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>2087</v>
       </c>
       <c r="H10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -7627,7 +7631,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -7644,7 +7648,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -7663,39 +7667,39 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>350</v>
       </c>
       <c r="B15" t="s">
         <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>347</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>347</v>
       </c>
       <c r="H15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -7712,7 +7716,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -7729,7 +7733,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -7746,7 +7750,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -7763,7 +7767,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>76</v>
       </c>
@@ -7780,7 +7784,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -7797,7 +7801,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -7808,7 +7812,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>82</v>
       </c>
@@ -7816,7 +7820,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -7830,7 +7834,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -7844,7 +7848,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -7858,7 +7862,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -7872,7 +7876,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>93</v>
       </c>
@@ -7886,7 +7890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>96</v>
       </c>
@@ -7900,7 +7904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>98</v>
       </c>
@@ -7914,7 +7918,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>100</v>
       </c>
@@ -7928,7 +7932,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -7942,7 +7946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>105</v>
       </c>
@@ -7956,7 +7960,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -7970,7 +7974,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>109</v>
       </c>
@@ -7984,7 +7988,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>111</v>
       </c>
@@ -7998,7 +8002,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>113</v>
       </c>
@@ -8012,7 +8016,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>115</v>
       </c>
@@ -8026,7 +8030,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>117</v>
       </c>
@@ -8040,7 +8044,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>119</v>
       </c>
@@ -8054,7 +8058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>121</v>
       </c>
@@ -8068,7 +8072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -8082,7 +8086,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -8096,7 +8100,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>128</v>
       </c>
@@ -8113,7 +8117,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>131</v>
       </c>
@@ -8130,7 +8134,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -8147,7 +8151,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -8164,7 +8168,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>139</v>
       </c>
@@ -8181,7 +8185,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>142</v>
       </c>
@@ -8198,7 +8202,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -8215,7 +8219,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>148</v>
       </c>
@@ -8232,7 +8236,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>151</v>
       </c>
@@ -8249,7 +8253,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>153</v>
       </c>
@@ -8266,7 +8270,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>156</v>
       </c>
@@ -8289,7 +8293,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>158</v>
       </c>
@@ -8312,7 +8316,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>160</v>
       </c>
@@ -8335,7 +8339,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>162</v>
       </c>
@@ -8358,7 +8362,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>164</v>
       </c>
@@ -8381,7 +8385,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>166</v>
       </c>
@@ -8404,7 +8408,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>168</v>
       </c>
@@ -8427,7 +8431,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>170</v>
       </c>
@@ -8450,7 +8454,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>172</v>
       </c>
@@ -8473,7 +8477,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>174</v>
       </c>
@@ -8496,7 +8500,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>176</v>
       </c>
@@ -8519,7 +8523,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>178</v>
       </c>
@@ -8542,7 +8546,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>180</v>
       </c>
@@ -8565,7 +8569,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>182</v>
       </c>
@@ -8588,7 +8592,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>184</v>
       </c>
@@ -8611,7 +8615,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>186</v>
       </c>
@@ -8634,7 +8638,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>188</v>
       </c>
@@ -8657,7 +8661,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>190</v>
       </c>
@@ -8680,7 +8684,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>192</v>
       </c>
@@ -8703,7 +8707,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>194</v>
       </c>
@@ -8726,7 +8730,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>196</v>
       </c>
@@ -8749,7 +8753,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>198</v>
       </c>
@@ -8772,7 +8776,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>200</v>
       </c>
@@ -8795,7 +8799,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>202</v>
       </c>
@@ -8818,7 +8822,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>204</v>
       </c>
@@ -8841,7 +8845,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>206</v>
       </c>
@@ -8864,7 +8868,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>208</v>
       </c>
@@ -8887,7 +8891,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>210</v>
       </c>
@@ -8910,7 +8914,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>212</v>
       </c>
@@ -8933,7 +8937,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>214</v>
       </c>
@@ -8956,7 +8960,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>216</v>
       </c>
@@ -8979,7 +8983,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>218</v>
       </c>
@@ -9002,7 +9006,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>220</v>
       </c>
@@ -9025,7 +9029,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>222</v>
       </c>
@@ -9048,7 +9052,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>224</v>
       </c>
@@ -9071,7 +9075,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>226</v>
       </c>
@@ -9094,7 +9098,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>228</v>
       </c>
@@ -9117,7 +9121,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>230</v>
       </c>
@@ -9140,7 +9144,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>232</v>
       </c>
@@ -9163,7 +9167,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>234</v>
       </c>
@@ -9186,7 +9190,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>236</v>
       </c>
@@ -9209,7 +9213,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>238</v>
       </c>
@@ -9232,7 +9236,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>240</v>
       </c>
@@ -9255,7 +9259,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>242</v>
       </c>
@@ -9278,7 +9282,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>244</v>
       </c>
@@ -9301,7 +9305,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>246</v>
       </c>
@@ -9324,7 +9328,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>248</v>
       </c>
@@ -9347,7 +9351,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>250</v>
       </c>
@@ -9370,7 +9374,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>252</v>
       </c>
@@ -9393,7 +9397,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>254</v>
       </c>
@@ -9416,7 +9420,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>256</v>
       </c>
@@ -9439,7 +9443,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>258</v>
       </c>
@@ -9462,7 +9466,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>260</v>
       </c>
@@ -9485,7 +9489,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>262</v>
       </c>
@@ -9508,7 +9512,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>264</v>
       </c>
@@ -9531,7 +9535,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>266</v>
       </c>
@@ -9554,7 +9558,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>268</v>
       </c>
@@ -9577,7 +9581,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>270</v>
       </c>
@@ -9600,7 +9604,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>272</v>
       </c>
@@ -9623,7 +9627,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>274</v>
       </c>
@@ -9646,7 +9650,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>276</v>
       </c>
@@ -9669,7 +9673,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>278</v>
       </c>
@@ -9692,7 +9696,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>280</v>
       </c>
@@ -9715,7 +9719,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>282</v>
       </c>
@@ -9738,7 +9742,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>284</v>
       </c>
@@ -9761,7 +9765,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>286</v>
       </c>
@@ -9784,7 +9788,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>288</v>
       </c>
@@ -9807,7 +9811,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>290</v>
       </c>
@@ -9830,7 +9834,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>292</v>
       </c>
@@ -9853,7 +9857,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>294</v>
       </c>
@@ -9876,7 +9880,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>296</v>
       </c>
@@ -9899,7 +9903,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>298</v>
       </c>
@@ -9922,7 +9926,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>300</v>
       </c>
@@ -9945,7 +9949,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>302</v>
       </c>
@@ -9968,7 +9972,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>304</v>
       </c>
@@ -9991,7 +9995,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>306</v>
       </c>
@@ -10014,7 +10018,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>308</v>
       </c>
@@ -10037,7 +10041,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>310</v>
       </c>
@@ -10060,7 +10064,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>312</v>
       </c>
@@ -10083,7 +10087,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>314</v>
       </c>
@@ -10106,7 +10110,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>316</v>
       </c>
@@ -10129,7 +10133,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>319</v>
       </c>
@@ -10152,7 +10156,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>321</v>
       </c>
@@ -10175,7 +10179,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>323</v>
       </c>
@@ -10198,7 +10202,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>326</v>
       </c>
@@ -10221,7 +10225,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>328</v>
       </c>
@@ -10244,7 +10248,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>331</v>
       </c>
@@ -10267,7 +10271,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>333</v>
       </c>
@@ -10290,7 +10294,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>335</v>
       </c>
@@ -10313,7 +10317,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>337</v>
       </c>
@@ -10336,7 +10340,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>339</v>
       </c>
@@ -10355,73 +10359,73 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B145" t="s">
         <v>343</v>
       </c>
       <c r="C145" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F145" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H145" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>346</v>
+        <v>638</v>
       </c>
       <c r="B146" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="C146" t="s">
-        <v>347</v>
+        <v>639</v>
       </c>
       <c r="F146" t="s">
-        <v>347</v>
+        <v>639</v>
       </c>
       <c r="H146" t="s">
-        <v>348</v>
+        <v>640</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>349</v>
+        <v>1479</v>
       </c>
       <c r="B147" t="s">
-        <v>58</v>
+        <v>461</v>
       </c>
       <c r="C147" t="s">
-        <v>344</v>
+        <v>1480</v>
       </c>
       <c r="F147" t="s">
-        <v>344</v>
+        <v>2096</v>
       </c>
       <c r="H147" t="s">
-        <v>345</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="B148" t="s">
-        <v>58</v>
+        <v>364</v>
       </c>
       <c r="C148" t="s">
-        <v>347</v>
+        <v>2082</v>
       </c>
       <c r="F148" t="s">
-        <v>347</v>
+        <v>2082</v>
       </c>
       <c r="H148" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>351</v>
       </c>
@@ -10435,7 +10439,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>354</v>
       </c>
@@ -10449,7 +10453,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>355</v>
       </c>
@@ -10463,7 +10467,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>358</v>
       </c>
@@ -10477,7 +10481,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>360</v>
       </c>
@@ -10496,22 +10500,22 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>363</v>
+        <v>612</v>
       </c>
       <c r="B154" t="s">
-        <v>364</v>
+        <v>613</v>
       </c>
       <c r="C154" t="s">
-        <v>365</v>
+        <v>607</v>
       </c>
       <c r="F154" t="s">
-        <v>365</v>
+        <v>607</v>
       </c>
       <c r="H154" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>367</v>
       </c>
@@ -10530,73 +10534,73 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>371</v>
+        <v>606</v>
       </c>
       <c r="B156" t="s">
-        <v>372</v>
+        <v>58</v>
       </c>
       <c r="C156" t="s">
-        <v>365</v>
+        <v>607</v>
       </c>
       <c r="F156" t="s">
-        <v>2080</v>
+        <v>607</v>
       </c>
       <c r="H156" t="s">
-        <v>373</v>
+        <v>608</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B157" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C157" t="s">
-        <v>365</v>
+        <v>2103</v>
       </c>
       <c r="F157" t="s">
-        <v>2081</v>
+        <v>2103</v>
       </c>
       <c r="H157" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="B158" t="s">
-        <v>377</v>
+        <v>475</v>
       </c>
       <c r="C158" t="s">
-        <v>378</v>
+        <v>476</v>
       </c>
       <c r="F158" t="s">
-        <v>378</v>
+        <v>476</v>
       </c>
       <c r="H158" t="s">
-        <v>379</v>
+        <v>477</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>380</v>
+        <v>479</v>
       </c>
       <c r="B159" t="s">
-        <v>364</v>
+        <v>58</v>
       </c>
       <c r="C159" t="s">
-        <v>365</v>
+        <v>476</v>
       </c>
       <c r="F159" t="s">
-        <v>2103</v>
+        <v>476</v>
       </c>
       <c r="H159" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>382</v>
       </c>
@@ -10610,7 +10614,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>384</v>
       </c>
@@ -10627,7 +10631,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>386</v>
       </c>
@@ -10646,56 +10650,56 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B163" t="s">
         <v>372</v>
       </c>
       <c r="C163" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="F163" t="s">
-        <v>390</v>
+        <v>2080</v>
       </c>
       <c r="H163" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>392</v>
+        <v>460</v>
       </c>
       <c r="B164" t="s">
-        <v>364</v>
+        <v>461</v>
       </c>
       <c r="C164" t="s">
-        <v>393</v>
+        <v>462</v>
       </c>
       <c r="F164" t="s">
-        <v>393</v>
+        <v>2085</v>
       </c>
       <c r="H164" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>395</v>
+        <v>38</v>
       </c>
       <c r="B165" t="s">
-        <v>364</v>
+        <v>39</v>
       </c>
       <c r="C165" t="s">
-        <v>365</v>
+        <v>40</v>
       </c>
       <c r="F165" t="s">
-        <v>2082</v>
+        <v>41</v>
       </c>
       <c r="H165" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>397</v>
       </c>
@@ -10712,7 +10716,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>400</v>
       </c>
@@ -10729,7 +10733,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>403</v>
       </c>
@@ -10743,7 +10747,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>406</v>
       </c>
@@ -10757,7 +10761,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>408</v>
       </c>
@@ -10773,39 +10777,39 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>410</v>
+        <v>773</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>770</v>
       </c>
       <c r="C171" t="s">
-        <v>411</v>
+        <v>774</v>
       </c>
       <c r="F171" t="s">
-        <v>2084</v>
+        <v>774</v>
       </c>
       <c r="H171" t="s">
-        <v>412</v>
+        <v>775</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>413</v>
+        <v>61</v>
       </c>
       <c r="B172" t="s">
-        <v>414</v>
+        <v>58</v>
       </c>
       <c r="C172" t="s">
-        <v>415</v>
+        <v>62</v>
       </c>
       <c r="F172" t="s">
-        <v>415</v>
+        <v>62</v>
       </c>
       <c r="H172" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>417</v>
       </c>
@@ -10816,7 +10820,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>420</v>
       </c>
@@ -10827,7 +10831,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>422</v>
       </c>
@@ -10844,7 +10848,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>425</v>
       </c>
@@ -10861,7 +10865,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>426</v>
       </c>
@@ -10878,7 +10882,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>429</v>
       </c>
@@ -10895,7 +10899,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>432</v>
       </c>
@@ -10903,7 +10907,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>433</v>
       </c>
@@ -10917,7 +10921,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>436</v>
       </c>
@@ -10931,7 +10935,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>438</v>
       </c>
@@ -10945,7 +10949,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>440</v>
       </c>
@@ -10959,7 +10963,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>442</v>
       </c>
@@ -10973,7 +10977,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>444</v>
       </c>
@@ -10987,7 +10991,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>446</v>
       </c>
@@ -11001,7 +11005,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>448</v>
       </c>
@@ -11015,7 +11019,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>450</v>
       </c>
@@ -11029,7 +11033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>452</v>
       </c>
@@ -11043,7 +11047,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>454</v>
       </c>
@@ -11057,7 +11061,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>456</v>
       </c>
@@ -11071,7 +11075,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>458</v>
       </c>
@@ -11087,56 +11091,56 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>460</v>
+        <v>686</v>
       </c>
       <c r="B193" t="s">
-        <v>461</v>
+        <v>676</v>
       </c>
       <c r="C193" t="s">
-        <v>462</v>
+        <v>687</v>
       </c>
       <c r="F193" t="s">
-        <v>2085</v>
+        <v>687</v>
       </c>
       <c r="H193" t="s">
-        <v>463</v>
+        <v>688</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>464</v>
+        <v>675</v>
       </c>
       <c r="B194" t="s">
-        <v>461</v>
+        <v>676</v>
       </c>
       <c r="C194" t="s">
-        <v>462</v>
+        <v>677</v>
       </c>
       <c r="F194" t="s">
-        <v>2086</v>
+        <v>677</v>
       </c>
       <c r="H194" t="s">
-        <v>465</v>
+        <v>678</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>466</v>
+        <v>679</v>
       </c>
       <c r="B195" t="s">
-        <v>461</v>
+        <v>676</v>
       </c>
       <c r="C195" t="s">
-        <v>462</v>
+        <v>680</v>
       </c>
       <c r="F195" t="s">
-        <v>2087</v>
+        <v>2075</v>
       </c>
       <c r="H195" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>468</v>
       </c>
@@ -11153,7 +11157,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>471</v>
       </c>
@@ -11172,22 +11176,22 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>474</v>
+        <v>682</v>
       </c>
       <c r="B198" t="s">
-        <v>475</v>
+        <v>676</v>
       </c>
       <c r="C198" t="s">
-        <v>476</v>
+        <v>683</v>
       </c>
       <c r="F198" t="s">
-        <v>476</v>
+        <v>2076</v>
       </c>
       <c r="H198" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>478</v>
       </c>
@@ -11197,39 +11201,39 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>479</v>
+        <v>645</v>
       </c>
       <c r="B200" t="s">
-        <v>58</v>
+        <v>364</v>
       </c>
       <c r="C200" t="s">
-        <v>476</v>
+        <v>646</v>
       </c>
       <c r="F200" t="s">
-        <v>476</v>
+        <v>646</v>
       </c>
       <c r="H200" t="s">
-        <v>477</v>
+        <v>647</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>480</v>
+        <v>1470</v>
       </c>
       <c r="B201" t="s">
-        <v>58</v>
+        <v>414</v>
       </c>
       <c r="C201" t="s">
-        <v>481</v>
+        <v>1468</v>
       </c>
       <c r="F201" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="H201" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>483</v>
       </c>
@@ -11243,7 +11247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>486</v>
       </c>
@@ -11257,7 +11261,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>488</v>
       </c>
@@ -11274,7 +11278,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>491</v>
       </c>
@@ -11291,7 +11295,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>494</v>
       </c>
@@ -11308,12 +11312,12 @@
         <v>497</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>499</v>
       </c>
@@ -11330,7 +11334,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>502</v>
       </c>
@@ -11347,7 +11351,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>505</v>
       </c>
@@ -11355,7 +11359,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>506</v>
       </c>
@@ -11372,7 +11376,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>509</v>
       </c>
@@ -11389,7 +11393,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>512</v>
       </c>
@@ -11403,7 +11407,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>515</v>
       </c>
@@ -11417,7 +11421,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>518</v>
       </c>
@@ -11431,7 +11435,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>520</v>
       </c>
@@ -11445,7 +11449,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>523</v>
       </c>
@@ -11459,7 +11463,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>525</v>
       </c>
@@ -11473,7 +11477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>527</v>
       </c>
@@ -11487,7 +11491,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>529</v>
       </c>
@@ -11501,7 +11505,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>531</v>
       </c>
@@ -11515,7 +11519,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>533</v>
       </c>
@@ -11529,7 +11533,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>535</v>
       </c>
@@ -11543,7 +11547,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>537</v>
       </c>
@@ -11557,7 +11561,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>539</v>
       </c>
@@ -11571,7 +11575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>541</v>
       </c>
@@ -11585,7 +11589,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>543</v>
       </c>
@@ -11595,27 +11599,27 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>544</v>
+        <v>1475</v>
       </c>
       <c r="B228" t="s">
         <v>414</v>
       </c>
       <c r="C228" t="s">
-        <v>545</v>
+        <v>1473</v>
       </c>
       <c r="F228" t="s">
-        <v>545</v>
+        <v>2095</v>
       </c>
       <c r="H228" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>548</v>
       </c>
@@ -11623,7 +11627,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>549</v>
       </c>
@@ -11631,12 +11635,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>552</v>
       </c>
@@ -11644,7 +11648,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>553</v>
       </c>
@@ -11652,12 +11656,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>556</v>
       </c>
@@ -11665,7 +11669,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>557</v>
       </c>
@@ -11673,12 +11677,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>559</v>
       </c>
@@ -11686,7 +11690,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>560</v>
       </c>
@@ -11694,12 +11698,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>562</v>
       </c>
@@ -11707,7 +11711,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>563</v>
       </c>
@@ -11715,12 +11719,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>566</v>
       </c>
@@ -11728,7 +11732,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>567</v>
       </c>
@@ -11736,12 +11740,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>570</v>
       </c>
@@ -11749,7 +11753,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>571</v>
       </c>
@@ -11757,12 +11761,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>573</v>
       </c>
@@ -11770,7 +11774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>574</v>
       </c>
@@ -11778,12 +11782,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>576</v>
       </c>
@@ -11791,7 +11795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>577</v>
       </c>
@@ -11799,12 +11803,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>579</v>
       </c>
@@ -11812,7 +11816,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>580</v>
       </c>
@@ -11820,12 +11824,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>582</v>
       </c>
@@ -11833,7 +11837,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>583</v>
       </c>
@@ -11841,7 +11845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>584</v>
       </c>
@@ -11849,7 +11853,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>585</v>
       </c>
@@ -11857,12 +11861,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>588</v>
       </c>
@@ -11870,7 +11874,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>589</v>
       </c>
@@ -11878,12 +11882,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>592</v>
       </c>
@@ -11891,7 +11895,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>593</v>
       </c>
@@ -11899,12 +11903,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>595</v>
       </c>
@@ -11912,7 +11916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>596</v>
       </c>
@@ -11920,12 +11924,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>598</v>
       </c>
@@ -11933,7 +11937,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>599</v>
       </c>
@@ -11941,12 +11945,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>602</v>
       </c>
@@ -11954,7 +11958,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>603</v>
       </c>
@@ -11962,7 +11966,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>604</v>
       </c>
@@ -11970,7 +11974,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>605</v>
       </c>
@@ -11980,22 +11984,22 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>606</v>
+        <v>729</v>
       </c>
       <c r="B281" t="s">
-        <v>58</v>
+        <v>730</v>
       </c>
       <c r="C281" t="s">
-        <v>607</v>
+        <v>731</v>
       </c>
       <c r="F281" t="s">
-        <v>607</v>
+        <v>731</v>
       </c>
       <c r="H281" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>609</v>
       </c>
@@ -12012,7 +12016,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>611</v>
       </c>
@@ -12031,73 +12035,73 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>612</v>
+        <v>767</v>
       </c>
       <c r="B284" t="s">
-        <v>613</v>
+        <v>730</v>
       </c>
       <c r="C284" t="s">
-        <v>607</v>
+        <v>737</v>
       </c>
       <c r="F284" t="s">
-        <v>607</v>
+        <v>737</v>
       </c>
       <c r="H284" t="s">
-        <v>608</v>
+        <v>738</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>614</v>
+        <v>736</v>
       </c>
       <c r="B285" t="s">
-        <v>372</v>
+        <v>58</v>
       </c>
       <c r="C285" t="s">
-        <v>615</v>
+        <v>737</v>
       </c>
       <c r="F285" t="s">
-        <v>615</v>
+        <v>737</v>
       </c>
       <c r="H285" t="s">
-        <v>616</v>
+        <v>738</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>617</v>
+        <v>758</v>
       </c>
       <c r="B286" t="s">
-        <v>39</v>
+        <v>730</v>
       </c>
       <c r="C286" t="s">
-        <v>618</v>
+        <v>740</v>
       </c>
       <c r="F286" t="s">
-        <v>2109</v>
+        <v>740</v>
       </c>
       <c r="H286" t="s">
-        <v>591</v>
+        <v>741</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>619</v>
+        <v>739</v>
       </c>
       <c r="B287" t="s">
-        <v>364</v>
+        <v>58</v>
       </c>
       <c r="C287" t="s">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="F287" t="s">
-        <v>620</v>
+        <v>740</v>
       </c>
       <c r="H287" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>622</v>
       </c>
@@ -12114,7 +12118,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>624</v>
       </c>
@@ -12131,7 +12135,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>625</v>
       </c>
@@ -12148,7 +12152,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>627</v>
       </c>
@@ -12165,7 +12169,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>629</v>
       </c>
@@ -12184,61 +12188,61 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>631</v>
+        <v>759</v>
       </c>
       <c r="B293" t="s">
-        <v>372</v>
+        <v>730</v>
       </c>
       <c r="C293" t="s">
-        <v>632</v>
+        <v>743</v>
       </c>
       <c r="F293" t="s">
-        <v>632</v>
+        <v>743</v>
       </c>
       <c r="H293" t="s">
-        <v>633</v>
+        <v>744</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>634</v>
+        <v>742</v>
       </c>
       <c r="B294" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C294" t="s">
-        <v>635</v>
+        <v>743</v>
       </c>
       <c r="F294" t="s">
-        <v>2111</v>
+        <v>743</v>
       </c>
       <c r="H294" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="B296" t="s">
-        <v>372</v>
+        <v>730</v>
       </c>
       <c r="C296" t="s">
-        <v>639</v>
+        <v>746</v>
       </c>
       <c r="F296" t="s">
-        <v>639</v>
+        <v>746</v>
       </c>
       <c r="H296" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>641</v>
       </c>
@@ -12246,17 +12250,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>644</v>
       </c>
@@ -12266,66 +12270,66 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>645</v>
+        <v>745</v>
       </c>
       <c r="B301" t="s">
-        <v>364</v>
+        <v>58</v>
       </c>
       <c r="C301" t="s">
-        <v>646</v>
+        <v>746</v>
       </c>
       <c r="F301" t="s">
-        <v>646</v>
+        <v>746</v>
       </c>
       <c r="H301" t="s">
-        <v>647</v>
+        <v>747</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>648</v>
+        <v>733</v>
       </c>
       <c r="B302" t="s">
-        <v>364</v>
+        <v>730</v>
       </c>
       <c r="C302" t="s">
-        <v>649</v>
+        <v>734</v>
       </c>
       <c r="F302" t="s">
-        <v>649</v>
+        <v>734</v>
       </c>
       <c r="H302" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>653</v>
+        <v>748</v>
       </c>
       <c r="B305" t="s">
-        <v>377</v>
+        <v>58</v>
       </c>
       <c r="C305" t="s">
-        <v>654</v>
+        <v>734</v>
       </c>
       <c r="F305" t="s">
-        <v>654</v>
+        <v>734</v>
       </c>
       <c r="H305" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>656</v>
       </c>
@@ -12339,7 +12343,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>659</v>
       </c>
@@ -12358,39 +12362,39 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>662</v>
+        <v>762</v>
       </c>
       <c r="B308" t="s">
-        <v>377</v>
+        <v>730</v>
       </c>
       <c r="C308" t="s">
-        <v>663</v>
+        <v>750</v>
       </c>
       <c r="F308" t="s">
-        <v>663</v>
+        <v>750</v>
       </c>
       <c r="H308" t="s">
-        <v>664</v>
+        <v>751</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>665</v>
+        <v>749</v>
       </c>
       <c r="B309" t="s">
-        <v>377</v>
+        <v>58</v>
       </c>
       <c r="C309" t="s">
-        <v>654</v>
+        <v>750</v>
       </c>
       <c r="F309" t="s">
-        <v>654</v>
+        <v>750</v>
       </c>
       <c r="H309" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>667</v>
       </c>
@@ -12398,7 +12402,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>668</v>
       </c>
@@ -12415,7 +12419,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>669</v>
       </c>
@@ -12432,7 +12436,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>671</v>
       </c>
@@ -12451,78 +12455,78 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>672</v>
+        <v>763</v>
       </c>
       <c r="B314" t="s">
-        <v>377</v>
+        <v>730</v>
       </c>
       <c r="C314" t="s">
-        <v>654</v>
+        <v>753</v>
       </c>
       <c r="F314" t="s">
-        <v>2108</v>
+        <v>753</v>
       </c>
       <c r="H314" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>674</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>675</v>
+        <v>752</v>
       </c>
       <c r="B316" t="s">
-        <v>676</v>
+        <v>58</v>
       </c>
       <c r="C316" t="s">
-        <v>677</v>
+        <v>753</v>
       </c>
       <c r="F316" t="s">
-        <v>677</v>
+        <v>753</v>
       </c>
       <c r="H316" t="s">
-        <v>678</v>
+        <v>754</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>679</v>
+        <v>764</v>
       </c>
       <c r="B317" t="s">
-        <v>676</v>
+        <v>730</v>
       </c>
       <c r="C317" t="s">
-        <v>680</v>
+        <v>756</v>
       </c>
       <c r="F317" t="s">
-        <v>2075</v>
+        <v>756</v>
       </c>
       <c r="H317" t="s">
-        <v>681</v>
+        <v>757</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>682</v>
+        <v>755</v>
       </c>
       <c r="B318" t="s">
-        <v>676</v>
+        <v>58</v>
       </c>
       <c r="C318" t="s">
-        <v>683</v>
+        <v>756</v>
       </c>
       <c r="F318" t="s">
-        <v>2076</v>
+        <v>756</v>
       </c>
       <c r="H318" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>685</v>
       </c>
@@ -12532,22 +12536,22 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>686</v>
+        <v>363</v>
       </c>
       <c r="B320" t="s">
-        <v>676</v>
+        <v>364</v>
       </c>
       <c r="C320" t="s">
-        <v>687</v>
+        <v>365</v>
       </c>
       <c r="F320" t="s">
-        <v>687</v>
+        <v>365</v>
       </c>
       <c r="H320" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>689</v>
       </c>
@@ -12564,7 +12568,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>693</v>
       </c>
@@ -12581,7 +12585,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>697</v>
       </c>
@@ -12598,7 +12602,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>700</v>
       </c>
@@ -12615,7 +12619,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>703</v>
       </c>
@@ -12632,7 +12636,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>707</v>
       </c>
@@ -12649,7 +12653,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>708</v>
       </c>
@@ -12666,7 +12670,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>709</v>
       </c>
@@ -12683,7 +12687,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>710</v>
       </c>
@@ -12700,7 +12704,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>711</v>
       </c>
@@ -12717,7 +12721,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>712</v>
       </c>
@@ -12734,7 +12738,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>713</v>
       </c>
@@ -12751,7 +12755,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>714</v>
       </c>
@@ -12768,7 +12772,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>715</v>
       </c>
@@ -12785,7 +12789,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>716</v>
       </c>
@@ -12802,7 +12806,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>717</v>
       </c>
@@ -12819,7 +12823,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>718</v>
       </c>
@@ -12836,7 +12840,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>719</v>
       </c>
@@ -12853,7 +12857,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>720</v>
       </c>
@@ -12870,7 +12874,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>721</v>
       </c>
@@ -12878,7 +12882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>722</v>
       </c>
@@ -12886,7 +12890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>723</v>
       </c>
@@ -12894,7 +12898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>724</v>
       </c>
@@ -12902,7 +12906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>725</v>
       </c>
@@ -12910,7 +12914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>726</v>
       </c>
@@ -12918,7 +12922,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>727</v>
       </c>
@@ -12926,7 +12930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>728</v>
       </c>
@@ -12936,226 +12940,226 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>729</v>
+        <v>349</v>
       </c>
       <c r="B348" t="s">
-        <v>730</v>
+        <v>58</v>
       </c>
       <c r="C348" t="s">
-        <v>731</v>
+        <v>344</v>
       </c>
       <c r="F348" t="s">
-        <v>731</v>
+        <v>344</v>
       </c>
       <c r="H348" t="s">
-        <v>732</v>
+        <v>345</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>733</v>
+        <v>342</v>
       </c>
       <c r="B349" t="s">
-        <v>730</v>
+        <v>343</v>
       </c>
       <c r="C349" t="s">
-        <v>734</v>
+        <v>344</v>
       </c>
       <c r="F349" t="s">
-        <v>734</v>
+        <v>344</v>
       </c>
       <c r="H349" t="s">
-        <v>735</v>
+        <v>345</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>736</v>
+        <v>57</v>
       </c>
       <c r="B350" t="s">
         <v>58</v>
       </c>
       <c r="C350" t="s">
-        <v>737</v>
+        <v>59</v>
       </c>
       <c r="F350" t="s">
-        <v>737</v>
+        <v>59</v>
       </c>
       <c r="H350" t="s">
-        <v>738</v>
+        <v>60</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>739</v>
+        <v>544</v>
       </c>
       <c r="B351" t="s">
-        <v>58</v>
+        <v>414</v>
       </c>
       <c r="C351" t="s">
-        <v>740</v>
+        <v>545</v>
       </c>
       <c r="F351" t="s">
-        <v>740</v>
+        <v>545</v>
       </c>
       <c r="H351" t="s">
-        <v>741</v>
+        <v>546</v>
       </c>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>742</v>
+        <v>785</v>
       </c>
       <c r="B352" t="s">
-        <v>58</v>
+        <v>414</v>
       </c>
       <c r="C352" t="s">
-        <v>743</v>
+        <v>786</v>
       </c>
       <c r="F352" t="s">
-        <v>743</v>
+        <v>786</v>
       </c>
       <c r="H352" t="s">
-        <v>744</v>
+        <v>787</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
       <c r="B353" t="s">
-        <v>58</v>
+        <v>414</v>
       </c>
       <c r="C353" t="s">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="F353" t="s">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="H353" t="s">
-        <v>747</v>
+        <v>784</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>748</v>
+        <v>413</v>
       </c>
       <c r="B354" t="s">
-        <v>58</v>
+        <v>414</v>
       </c>
       <c r="C354" t="s">
-        <v>734</v>
+        <v>415</v>
       </c>
       <c r="F354" t="s">
-        <v>734</v>
+        <v>415</v>
       </c>
       <c r="H354" t="s">
-        <v>735</v>
+        <v>416</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
       <c r="B355" t="s">
-        <v>58</v>
+        <v>414</v>
       </c>
       <c r="C355" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="F355" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="H355" t="s">
-        <v>751</v>
+        <v>781</v>
       </c>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>752</v>
+        <v>672</v>
       </c>
       <c r="B356" t="s">
-        <v>58</v>
+        <v>377</v>
       </c>
       <c r="C356" t="s">
-        <v>753</v>
+        <v>654</v>
       </c>
       <c r="F356" t="s">
-        <v>753</v>
+        <v>2108</v>
       </c>
       <c r="H356" t="s">
-        <v>754</v>
+        <v>673</v>
       </c>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>755</v>
+        <v>653</v>
       </c>
       <c r="B357" t="s">
-        <v>58</v>
+        <v>377</v>
       </c>
       <c r="C357" t="s">
-        <v>756</v>
+        <v>654</v>
       </c>
       <c r="F357" t="s">
-        <v>756</v>
+        <v>654</v>
       </c>
       <c r="H357" t="s">
-        <v>757</v>
+        <v>655</v>
       </c>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>758</v>
+        <v>662</v>
       </c>
       <c r="B358" t="s">
-        <v>730</v>
+        <v>377</v>
       </c>
       <c r="C358" t="s">
-        <v>740</v>
+        <v>663</v>
       </c>
       <c r="F358" t="s">
-        <v>740</v>
+        <v>663</v>
       </c>
       <c r="H358" t="s">
-        <v>741</v>
+        <v>664</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>759</v>
+        <v>665</v>
       </c>
       <c r="B359" t="s">
-        <v>730</v>
+        <v>377</v>
       </c>
       <c r="C359" t="s">
-        <v>743</v>
+        <v>2317</v>
       </c>
       <c r="F359" t="s">
-        <v>743</v>
+        <v>2317</v>
       </c>
       <c r="H359" t="s">
-        <v>744</v>
+        <v>666</v>
       </c>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>760</v>
+        <v>376</v>
       </c>
       <c r="B360" t="s">
-        <v>730</v>
+        <v>377</v>
       </c>
       <c r="C360" t="s">
-        <v>746</v>
+        <v>378</v>
       </c>
       <c r="F360" t="s">
-        <v>746</v>
+        <v>378</v>
       </c>
       <c r="H360" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>761</v>
       </c>
@@ -13165,56 +13169,56 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>762</v>
+        <v>619</v>
       </c>
       <c r="B362" t="s">
-        <v>730</v>
+        <v>364</v>
       </c>
       <c r="C362" t="s">
-        <v>750</v>
+        <v>620</v>
       </c>
       <c r="F362" t="s">
-        <v>750</v>
+        <v>620</v>
       </c>
       <c r="H362" t="s">
-        <v>751</v>
+        <v>621</v>
       </c>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="B363" t="s">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="C363" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F363" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="H363" t="s">
-        <v>754</v>
+        <v>772</v>
       </c>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>764</v>
+        <v>634</v>
       </c>
       <c r="B364" t="s">
-        <v>730</v>
+        <v>39</v>
       </c>
       <c r="C364" t="s">
-        <v>756</v>
+        <v>635</v>
       </c>
       <c r="F364" t="s">
-        <v>756</v>
+        <v>2111</v>
       </c>
       <c r="H364" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>765</v>
       </c>
@@ -13233,22 +13237,22 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>767</v>
+        <v>631</v>
       </c>
       <c r="B366" t="s">
-        <v>730</v>
+        <v>372</v>
       </c>
       <c r="C366" t="s">
-        <v>737</v>
+        <v>632</v>
       </c>
       <c r="F366" t="s">
-        <v>737</v>
+        <v>632</v>
       </c>
       <c r="H366" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>768</v>
       </c>
@@ -13258,39 +13262,39 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>769</v>
+        <v>1496</v>
       </c>
       <c r="B368" t="s">
-        <v>770</v>
+        <v>461</v>
       </c>
       <c r="C368" t="s">
-        <v>771</v>
+        <v>462</v>
       </c>
       <c r="F368" t="s">
-        <v>771</v>
+        <v>2098</v>
       </c>
       <c r="H368" t="s">
-        <v>772</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>773</v>
+        <v>1477</v>
       </c>
       <c r="B369" t="s">
-        <v>770</v>
+        <v>461</v>
       </c>
       <c r="C369" t="s">
-        <v>774</v>
+        <v>462</v>
       </c>
       <c r="F369" t="s">
-        <v>774</v>
+        <v>2097</v>
       </c>
       <c r="H369" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>776</v>
       </c>
@@ -13298,7 +13302,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>777</v>
       </c>
@@ -13314,56 +13318,56 @@
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>779</v>
+        <v>614</v>
       </c>
       <c r="B372" t="s">
-        <v>414</v>
+        <v>372</v>
       </c>
       <c r="C372" t="s">
-        <v>780</v>
+        <v>615</v>
       </c>
       <c r="F372" t="s">
-        <v>780</v>
+        <v>615</v>
       </c>
       <c r="H372" t="s">
-        <v>781</v>
+        <v>616</v>
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>782</v>
+        <v>617</v>
       </c>
       <c r="B373" t="s">
-        <v>414</v>
+        <v>39</v>
       </c>
       <c r="C373" t="s">
-        <v>783</v>
+        <v>618</v>
       </c>
       <c r="F373" t="s">
-        <v>783</v>
+        <v>2109</v>
       </c>
       <c r="H373" t="s">
-        <v>784</v>
+        <v>591</v>
       </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>785</v>
+        <v>410</v>
       </c>
       <c r="B374" t="s">
-        <v>414</v>
+        <v>39</v>
       </c>
       <c r="C374" t="s">
-        <v>786</v>
+        <v>411</v>
       </c>
       <c r="F374" t="s">
-        <v>786</v>
+        <v>2084</v>
       </c>
       <c r="H374" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>788</v>
       </c>
@@ -13371,7 +13375,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>789</v>
       </c>
@@ -13385,7 +13389,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>792</v>
       </c>
@@ -13399,7 +13403,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>794</v>
       </c>
@@ -13410,7 +13414,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>796</v>
       </c>
@@ -13433,7 +13437,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>802</v>
       </c>
@@ -13444,7 +13448,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>804</v>
       </c>
@@ -13467,7 +13471,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>809</v>
       </c>
@@ -13478,7 +13482,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>811</v>
       </c>
@@ -13501,7 +13505,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>816</v>
       </c>
@@ -13512,7 +13516,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>818</v>
       </c>
@@ -13535,7 +13539,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>823</v>
       </c>
@@ -13546,7 +13550,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>825</v>
       </c>
@@ -13569,7 +13573,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>830</v>
       </c>
@@ -13580,7 +13584,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>832</v>
       </c>
@@ -13603,7 +13607,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>837</v>
       </c>
@@ -13614,7 +13618,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>839</v>
       </c>
@@ -13637,7 +13641,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>844</v>
       </c>
@@ -13648,7 +13652,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>846</v>
       </c>
@@ -13671,7 +13675,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>851</v>
       </c>
@@ -13682,7 +13686,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>853</v>
       </c>
@@ -13705,7 +13709,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>858</v>
       </c>
@@ -13716,7 +13720,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>860</v>
       </c>
@@ -13739,7 +13743,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>866</v>
       </c>
@@ -13750,7 +13754,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>868</v>
       </c>
@@ -13773,7 +13777,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>873</v>
       </c>
@@ -13784,7 +13788,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>875</v>
       </c>
@@ -13807,7 +13811,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>881</v>
       </c>
@@ -13818,7 +13822,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>883</v>
       </c>
@@ -13841,7 +13845,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>889</v>
       </c>
@@ -13852,7 +13856,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>891</v>
       </c>
@@ -13875,7 +13879,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>897</v>
       </c>
@@ -13886,7 +13890,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>899</v>
       </c>
@@ -13909,7 +13913,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>904</v>
       </c>
@@ -13920,7 +13924,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>906</v>
       </c>
@@ -13943,7 +13947,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>911</v>
       </c>
@@ -13954,7 +13958,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>913</v>
       </c>
@@ -13977,7 +13981,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>919</v>
       </c>
@@ -13988,7 +13992,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>921</v>
       </c>
@@ -14011,7 +14015,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>927</v>
       </c>
@@ -14022,7 +14026,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>929</v>
       </c>
@@ -14045,7 +14049,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>934</v>
       </c>
@@ -14056,7 +14060,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>936</v>
       </c>
@@ -14079,7 +14083,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>941</v>
       </c>
@@ -14090,7 +14094,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>943</v>
       </c>
@@ -14113,7 +14117,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>948</v>
       </c>
@@ -14124,7 +14128,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>950</v>
       </c>
@@ -14147,7 +14151,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>955</v>
       </c>
@@ -14158,7 +14162,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>957</v>
       </c>
@@ -14181,7 +14185,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>962</v>
       </c>
@@ -14192,7 +14196,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>964</v>
       </c>
@@ -14215,7 +14219,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>970</v>
       </c>
@@ -14226,7 +14230,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>972</v>
       </c>
@@ -14249,7 +14253,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>978</v>
       </c>
@@ -14260,7 +14264,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>980</v>
       </c>
@@ -14283,7 +14287,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>985</v>
       </c>
@@ -14294,7 +14298,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>987</v>
       </c>
@@ -14317,7 +14321,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>992</v>
       </c>
@@ -14328,7 +14332,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>994</v>
       </c>
@@ -14351,7 +14355,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1000</v>
       </c>
@@ -14362,7 +14366,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1002</v>
       </c>
@@ -14385,7 +14389,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1008</v>
       </c>
@@ -14396,7 +14400,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1010</v>
       </c>
@@ -14419,7 +14423,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1016</v>
       </c>
@@ -14430,7 +14434,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1018</v>
       </c>
@@ -14453,7 +14457,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1023</v>
       </c>
@@ -14464,7 +14468,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1025</v>
       </c>
@@ -14487,7 +14491,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1030</v>
       </c>
@@ -14498,7 +14502,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1032</v>
       </c>
@@ -14521,7 +14525,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1038</v>
       </c>
@@ -14532,7 +14536,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1040</v>
       </c>
@@ -14555,7 +14559,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1045</v>
       </c>
@@ -14566,7 +14570,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1047</v>
       </c>
@@ -14589,7 +14593,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1052</v>
       </c>
@@ -14600,7 +14604,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1054</v>
       </c>
@@ -14623,7 +14627,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1059</v>
       </c>
@@ -14634,7 +14638,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1061</v>
       </c>
@@ -14657,7 +14661,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1066</v>
       </c>
@@ -14668,7 +14672,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1068</v>
       </c>
@@ -14691,7 +14695,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1073</v>
       </c>
@@ -14702,7 +14706,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1075</v>
       </c>
@@ -14725,7 +14729,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>1080</v>
       </c>
@@ -14736,7 +14740,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1082</v>
       </c>
@@ -14747,7 +14751,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1084</v>
       </c>
@@ -14770,7 +14774,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1089</v>
       </c>
@@ -14781,7 +14785,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1091</v>
       </c>
@@ -14804,7 +14808,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>1097</v>
       </c>
@@ -14815,7 +14819,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1099</v>
       </c>
@@ -14838,7 +14842,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>1104</v>
       </c>
@@ -14849,7 +14853,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1106</v>
       </c>
@@ -14872,7 +14876,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="465" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1111</v>
       </c>
@@ -14883,7 +14887,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1113</v>
       </c>
@@ -14906,7 +14910,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1118</v>
       </c>
@@ -14917,7 +14921,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1120</v>
       </c>
@@ -14940,7 +14944,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1125</v>
       </c>
@@ -14951,7 +14955,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1127</v>
       </c>
@@ -14974,7 +14978,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1132</v>
       </c>
@@ -14985,7 +14989,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1134</v>
       </c>
@@ -15008,7 +15012,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1139</v>
       </c>
@@ -15019,7 +15023,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="474" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1141</v>
       </c>
@@ -15042,7 +15046,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="475" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1147</v>
       </c>
@@ -15053,7 +15057,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1149</v>
       </c>
@@ -15076,7 +15080,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1155</v>
       </c>
@@ -15087,7 +15091,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1157</v>
       </c>
@@ -15110,7 +15114,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1162</v>
       </c>
@@ -15121,7 +15125,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1164</v>
       </c>
@@ -15144,7 +15148,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1169</v>
       </c>
@@ -15155,7 +15159,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1171</v>
       </c>
@@ -15178,7 +15182,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1177</v>
       </c>
@@ -15189,7 +15193,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1179</v>
       </c>
@@ -15212,7 +15216,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1185</v>
       </c>
@@ -15223,7 +15227,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1187</v>
       </c>
@@ -15246,7 +15250,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1192</v>
       </c>
@@ -15257,7 +15261,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1194</v>
       </c>
@@ -15280,7 +15284,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>1199</v>
       </c>
@@ -15291,7 +15295,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1201</v>
       </c>
@@ -15314,7 +15318,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1206</v>
       </c>
@@ -15325,7 +15329,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1208</v>
       </c>
@@ -15348,7 +15352,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1213</v>
       </c>
@@ -15359,7 +15363,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1215</v>
       </c>
@@ -15382,7 +15386,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1221</v>
       </c>
@@ -15393,7 +15397,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1223</v>
       </c>
@@ -15416,7 +15420,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1229</v>
       </c>
@@ -15427,7 +15431,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1231</v>
       </c>
@@ -15450,7 +15454,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1237</v>
       </c>
@@ -15461,7 +15465,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1239</v>
       </c>
@@ -15484,7 +15488,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1244</v>
       </c>
@@ -15495,7 +15499,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1246</v>
       </c>
@@ -15518,7 +15522,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1251</v>
       </c>
@@ -15529,7 +15533,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1253</v>
       </c>
@@ -15552,7 +15556,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>1258</v>
       </c>
@@ -15563,7 +15567,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1260</v>
       </c>
@@ -15586,7 +15590,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1265</v>
       </c>
@@ -15597,7 +15601,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1267</v>
       </c>
@@ -15620,7 +15624,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>1273</v>
       </c>
@@ -15631,7 +15635,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1275</v>
       </c>
@@ -15654,7 +15658,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>1280</v>
       </c>
@@ -15665,7 +15669,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1282</v>
       </c>
@@ -15688,7 +15692,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>1287</v>
       </c>
@@ -15699,7 +15703,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1289</v>
       </c>
@@ -15722,7 +15726,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>1295</v>
       </c>
@@ -15733,7 +15737,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>1297</v>
       </c>
@@ -15756,7 +15760,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>1302</v>
       </c>
@@ -15767,7 +15771,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1304</v>
       </c>
@@ -15790,7 +15794,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>1309</v>
       </c>
@@ -15801,7 +15805,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1311</v>
       </c>
@@ -15824,7 +15828,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>1316</v>
       </c>
@@ -15835,7 +15839,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1318</v>
       </c>
@@ -15858,7 +15862,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1324</v>
       </c>
@@ -15869,7 +15873,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1326</v>
       </c>
@@ -15892,7 +15896,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>1332</v>
       </c>
@@ -15903,7 +15907,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1334</v>
       </c>
@@ -15926,7 +15930,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1339</v>
       </c>
@@ -15937,7 +15941,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>1341</v>
       </c>
@@ -15960,7 +15964,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1346</v>
       </c>
@@ -15971,7 +15975,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1348</v>
       </c>
@@ -15994,7 +15998,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>1353</v>
       </c>
@@ -16005,7 +16009,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1355</v>
       </c>
@@ -16028,7 +16032,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>1360</v>
       </c>
@@ -16039,7 +16043,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>1362</v>
       </c>
@@ -16062,7 +16066,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>1367</v>
       </c>
@@ -16073,7 +16077,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>1369</v>
       </c>
@@ -16096,7 +16100,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>1374</v>
       </c>
@@ -16107,7 +16111,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1376</v>
       </c>
@@ -16130,7 +16134,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>1381</v>
       </c>
@@ -16141,7 +16145,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>1383</v>
       </c>
@@ -16164,7 +16168,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1388</v>
       </c>
@@ -16175,7 +16179,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>1390</v>
       </c>
@@ -16198,7 +16202,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1396</v>
       </c>
@@ -16209,7 +16213,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1398</v>
       </c>
@@ -16232,7 +16236,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>1403</v>
       </c>
@@ -16243,7 +16247,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1405</v>
       </c>
@@ -16266,7 +16270,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1411</v>
       </c>
@@ -16277,7 +16281,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1413</v>
       </c>
@@ -16300,7 +16304,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>1418</v>
       </c>
@@ -16311,7 +16315,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>1420</v>
       </c>
@@ -16334,7 +16338,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>1425</v>
       </c>
@@ -16345,7 +16349,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>1427</v>
       </c>
@@ -16368,7 +16372,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>1432</v>
       </c>
@@ -16379,7 +16383,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>1434</v>
       </c>
@@ -16402,7 +16406,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>1440</v>
       </c>
@@ -16410,7 +16414,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>1441</v>
       </c>
@@ -16424,7 +16428,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>1443</v>
       </c>
@@ -16438,7 +16442,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>1445</v>
       </c>
@@ -16452,7 +16456,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>1448</v>
       </c>
@@ -16466,7 +16470,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>1449</v>
       </c>
@@ -16480,7 +16484,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>1450</v>
       </c>
@@ -16494,7 +16498,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>1451</v>
       </c>
@@ -16508,7 +16512,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>1452</v>
       </c>
@@ -16516,7 +16520,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>1453</v>
       </c>
@@ -16530,7 +16534,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>1455</v>
       </c>
@@ -16544,7 +16548,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>1456</v>
       </c>
@@ -16558,7 +16562,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>1457</v>
       </c>
@@ -16572,7 +16576,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>1458</v>
       </c>
@@ -16586,7 +16590,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>1459</v>
       </c>
@@ -16600,7 +16604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>1460</v>
       </c>
@@ -16614,7 +16618,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>1461</v>
       </c>
@@ -16628,7 +16632,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>1462</v>
       </c>
@@ -16642,7 +16646,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>1463</v>
       </c>
@@ -16656,7 +16660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>1464</v>
       </c>
@@ -16670,7 +16674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>1465</v>
       </c>
@@ -16684,7 +16688,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>1466</v>
       </c>
@@ -16700,58 +16704,58 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>1467</v>
+        <v>464</v>
       </c>
       <c r="B577" t="s">
-        <v>414</v>
+        <v>461</v>
       </c>
       <c r="C577" t="s">
-        <v>1468</v>
+        <v>462</v>
       </c>
       <c r="F577" t="s">
-        <v>2093</v>
+        <v>2086</v>
       </c>
       <c r="H577" t="s">
-        <v>1469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1470</v>
+        <v>389</v>
       </c>
       <c r="B578" t="s">
-        <v>414</v>
+        <v>372</v>
       </c>
       <c r="C578" t="s">
-        <v>1468</v>
+        <v>390</v>
       </c>
       <c r="F578" t="s">
-        <v>2092</v>
+        <v>390</v>
       </c>
       <c r="H578" t="s">
-        <v>1471</v>
+        <v>391</v>
       </c>
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="B579" t="s">
         <v>414</v>
       </c>
       <c r="C579" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="F579" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="H579" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="B580" t="s">
         <v>414</v>
@@ -16760,47 +16764,47 @@
         <v>1473</v>
       </c>
       <c r="F580" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="H580" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1477</v>
+        <v>392</v>
       </c>
       <c r="B581" t="s">
-        <v>461</v>
+        <v>364</v>
       </c>
       <c r="C581" t="s">
-        <v>462</v>
+        <v>393</v>
       </c>
       <c r="F581" t="s">
-        <v>2097</v>
+        <v>393</v>
       </c>
       <c r="H581" t="s">
-        <v>1478</v>
+        <v>394</v>
       </c>
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>1479</v>
+        <v>480</v>
       </c>
       <c r="B582" t="s">
-        <v>461</v>
+        <v>58</v>
       </c>
       <c r="C582" t="s">
-        <v>1480</v>
+        <v>481</v>
       </c>
       <c r="F582" t="s">
-        <v>2096</v>
+        <v>2090</v>
       </c>
       <c r="H582" t="s">
-        <v>1481</v>
-      </c>
-    </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>1482</v>
       </c>
@@ -16814,7 +16818,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>1484</v>
       </c>
@@ -16828,7 +16832,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>1486</v>
       </c>
@@ -16845,7 +16849,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>1488</v>
       </c>
@@ -16862,7 +16866,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>1491</v>
       </c>
@@ -16879,7 +16883,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>1494</v>
       </c>
@@ -16898,22 +16902,22 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1496</v>
+        <v>648</v>
       </c>
       <c r="B589" t="s">
-        <v>461</v>
+        <v>364</v>
       </c>
       <c r="C589" t="s">
-        <v>462</v>
+        <v>649</v>
       </c>
       <c r="F589" t="s">
-        <v>2098</v>
+        <v>649</v>
       </c>
       <c r="H589" t="s">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>1498</v>
       </c>
@@ -16921,7 +16925,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>1499</v>
       </c>
@@ -16935,7 +16939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>1501</v>
       </c>
@@ -16949,7 +16953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>1503</v>
       </c>
@@ -16963,7 +16967,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>1505</v>
       </c>
@@ -16971,7 +16975,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>1506</v>
       </c>
@@ -16979,7 +16983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>1507</v>
       </c>
@@ -16987,7 +16991,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>1508</v>
       </c>
@@ -16995,7 +16999,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>1509</v>
       </c>
@@ -17003,7 +17007,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>1510</v>
       </c>
@@ -17011,7 +17015,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>1511</v>
       </c>
@@ -17019,7 +17023,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>1512</v>
       </c>
@@ -17027,7 +17031,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>1513</v>
       </c>
@@ -17035,7 +17039,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>1514</v>
       </c>
@@ -17043,7 +17047,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>1515</v>
       </c>
@@ -17051,7 +17055,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>1516</v>
       </c>
@@ -17059,7 +17063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>1517</v>
       </c>
@@ -17067,7 +17071,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>1518</v>
       </c>
@@ -17081,7 +17085,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>1520</v>
       </c>
@@ -17095,7 +17099,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>1521</v>
       </c>
@@ -17109,7 +17113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>1523</v>
       </c>
@@ -17123,7 +17127,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>1525</v>
       </c>
@@ -17137,7 +17141,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>1526</v>
       </c>
@@ -17151,7 +17155,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>1528</v>
       </c>
@@ -17165,7 +17169,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>1530</v>
       </c>
@@ -17173,7 +17177,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>1531</v>
       </c>
@@ -17187,7 +17191,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>1533</v>
       </c>
@@ -17201,7 +17205,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>1535</v>
       </c>
@@ -17215,7 +17219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>1537</v>
       </c>
@@ -17229,7 +17233,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>1539</v>
       </c>
@@ -17243,7 +17247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>1541</v>
       </c>
@@ -17257,7 +17261,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>1543</v>
       </c>
@@ -17271,7 +17275,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>1545</v>
       </c>
@@ -17285,7 +17289,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>1547</v>
       </c>
@@ -17299,7 +17303,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>1549</v>
       </c>
@@ -17313,7 +17317,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>1551</v>
       </c>
@@ -17327,7 +17331,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>1553</v>
       </c>
@@ -17341,7 +17345,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>1555</v>
       </c>
@@ -17355,7 +17359,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>1557</v>
       </c>
@@ -17363,7 +17367,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>1558</v>
       </c>
@@ -17377,7 +17381,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>1560</v>
       </c>
@@ -17391,7 +17395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>1562</v>
       </c>
@@ -17405,7 +17409,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>1564</v>
       </c>
@@ -17419,7 +17423,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>1566</v>
       </c>
@@ -17433,7 +17437,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>1568</v>
       </c>
@@ -17447,7 +17451,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>1570</v>
       </c>
@@ -17461,7 +17465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>1572</v>
       </c>
@@ -17475,7 +17479,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>1574</v>
       </c>
@@ -17489,7 +17493,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>1576</v>
       </c>
@@ -17503,7 +17507,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>1578</v>
       </c>
@@ -17517,7 +17521,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>1580</v>
       </c>
@@ -17531,7 +17535,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>1582</v>
       </c>
@@ -17545,7 +17549,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>1584</v>
       </c>
@@ -17553,7 +17557,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>1585</v>
       </c>
@@ -17567,7 +17571,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>1587</v>
       </c>
@@ -17575,7 +17579,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>1588</v>
       </c>
@@ -17589,7 +17593,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>1590</v>
       </c>
@@ -17603,7 +17607,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>1592</v>
       </c>
@@ -17617,7 +17621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>1594</v>
       </c>
@@ -17631,7 +17635,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>1596</v>
       </c>
@@ -17645,7 +17649,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>1598</v>
       </c>
@@ -17659,7 +17663,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>1600</v>
       </c>
@@ -17673,7 +17677,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>1602</v>
       </c>
@@ -17687,7 +17691,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>1604</v>
       </c>
@@ -17701,7 +17705,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>1606</v>
       </c>
@@ -17715,7 +17719,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>1608</v>
       </c>
@@ -17729,7 +17733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>1610</v>
       </c>
@@ -17737,7 +17741,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>1611</v>
       </c>
@@ -17751,7 +17755,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>1613</v>
       </c>
@@ -17765,7 +17769,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>1615</v>
       </c>
@@ -17779,7 +17783,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>1617</v>
       </c>
@@ -17793,7 +17797,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>1619</v>
       </c>
@@ -17807,7 +17811,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>1621</v>
       </c>
@@ -17821,7 +17825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>1623</v>
       </c>
@@ -17835,7 +17839,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>1625</v>
       </c>
@@ -17849,7 +17853,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>1627</v>
       </c>
@@ -17863,7 +17867,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>1629</v>
       </c>
@@ -17877,7 +17881,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>1631</v>
       </c>
@@ -17891,7 +17895,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>1633</v>
       </c>
@@ -17905,7 +17909,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>1635</v>
       </c>
@@ -17919,7 +17923,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>1637</v>
       </c>
@@ -17927,7 +17931,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>1638</v>
       </c>
@@ -17941,7 +17945,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>1640</v>
       </c>
@@ -17955,7 +17959,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>1642</v>
       </c>
@@ -17969,7 +17973,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>1644</v>
       </c>
@@ -17983,7 +17987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>1646</v>
       </c>
@@ -17997,7 +18001,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>1648</v>
       </c>
@@ -18011,7 +18015,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>1650</v>
       </c>
@@ -18025,7 +18029,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>1652</v>
       </c>
@@ -18039,7 +18043,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>1654</v>
       </c>
@@ -18053,7 +18057,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>1656</v>
       </c>
@@ -18067,7 +18071,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>1658</v>
       </c>
@@ -18081,7 +18085,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>1660</v>
       </c>
@@ -18095,7 +18099,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>1662</v>
       </c>
@@ -18109,7 +18113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>1664</v>
       </c>
@@ -18117,7 +18121,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>1665</v>
       </c>
@@ -18125,7 +18129,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>1666</v>
       </c>
@@ -18139,7 +18143,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>1668</v>
       </c>
@@ -18153,7 +18157,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>1670</v>
       </c>
@@ -18161,7 +18165,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>1671</v>
       </c>
@@ -18169,7 +18173,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>1672</v>
       </c>
@@ -18183,7 +18187,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>1674</v>
       </c>
@@ -18197,7 +18201,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>1676</v>
       </c>
@@ -18205,7 +18209,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>1677</v>
       </c>
@@ -18219,7 +18223,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>1679</v>
       </c>
@@ -18233,7 +18237,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>1681</v>
       </c>
@@ -18241,7 +18245,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>1682</v>
       </c>
@@ -18249,7 +18253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>1683</v>
       </c>
@@ -18263,7 +18267,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>1685</v>
       </c>
@@ -18277,7 +18281,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>1687</v>
       </c>
@@ -18285,7 +18289,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>1688</v>
       </c>
@@ -18293,7 +18297,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>1689</v>
       </c>
@@ -18307,7 +18311,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>1691</v>
       </c>
@@ -18321,7 +18325,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="703" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>1693</v>
       </c>
@@ -18329,7 +18333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>1694</v>
       </c>
@@ -18337,7 +18341,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>1695</v>
       </c>
@@ -18351,7 +18355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>1697</v>
       </c>
@@ -18365,7 +18369,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>1699</v>
       </c>
@@ -18373,7 +18377,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>1700</v>
       </c>
@@ -18381,7 +18385,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>1701</v>
       </c>
@@ -18395,7 +18399,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>1703</v>
       </c>
@@ -18409,7 +18413,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>1705</v>
       </c>
@@ -18417,7 +18421,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>1706</v>
       </c>
@@ -18425,7 +18429,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>1707</v>
       </c>
@@ -18439,7 +18443,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="714" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>1709</v>
       </c>
@@ -18453,7 +18457,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="715" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>1711</v>
       </c>
@@ -18461,7 +18465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="716" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>1712</v>
       </c>
@@ -18469,7 +18473,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="717" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>1713</v>
       </c>
@@ -18483,7 +18487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>1715</v>
       </c>
@@ -18497,7 +18501,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>1717</v>
       </c>
@@ -18505,7 +18509,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>1718</v>
       </c>
@@ -18513,7 +18517,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="721" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>1719</v>
       </c>
@@ -18527,7 +18531,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="722" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>1721</v>
       </c>
@@ -18541,7 +18545,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="723" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>1723</v>
       </c>
@@ -18549,7 +18553,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="724" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>1724</v>
       </c>
@@ -18557,7 +18561,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="725" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>1725</v>
       </c>
@@ -18571,7 +18575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="726" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>1727</v>
       </c>
@@ -18585,7 +18589,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="727" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>1729</v>
       </c>
@@ -18593,7 +18597,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="728" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>1730</v>
       </c>
@@ -18601,7 +18605,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="729" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>1731</v>
       </c>
@@ -18615,7 +18619,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="730" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>1733</v>
       </c>
@@ -18629,7 +18633,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="731" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>1735</v>
       </c>
@@ -18637,7 +18641,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="732" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>1736</v>
       </c>
@@ -18645,7 +18649,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="733" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>1737</v>
       </c>
@@ -18659,7 +18663,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="734" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>1739</v>
       </c>
@@ -18673,7 +18677,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="735" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>1741</v>
       </c>
@@ -18681,7 +18685,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="736" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>1742</v>
       </c>
@@ -18689,7 +18693,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="737" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>1743</v>
       </c>
@@ -18703,7 +18707,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="738" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>1745</v>
       </c>
@@ -18717,7 +18721,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="739" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>1747</v>
       </c>
@@ -18725,7 +18729,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="740" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>1748</v>
       </c>
@@ -18733,7 +18737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="741" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>1749</v>
       </c>
@@ -18747,7 +18751,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="742" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>1751</v>
       </c>
@@ -18761,7 +18765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="743" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>1753</v>
       </c>
@@ -18769,7 +18773,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="744" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>1754</v>
       </c>
@@ -18783,7 +18787,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="745" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>1756</v>
       </c>
@@ -18791,7 +18795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="746" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>1757</v>
       </c>
@@ -18805,7 +18809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="747" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>1760</v>
       </c>
@@ -18819,7 +18823,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="748" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>1762</v>
       </c>
@@ -18833,7 +18837,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="749" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>1764</v>
       </c>
@@ -18847,7 +18851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="750" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>1766</v>
       </c>
@@ -18861,7 +18865,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="751" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>1768</v>
       </c>
@@ -18875,7 +18879,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="752" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>1770</v>
       </c>
@@ -18889,7 +18893,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>1772</v>
       </c>
@@ -18903,7 +18907,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>1774</v>
       </c>
@@ -18917,7 +18921,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>1776</v>
       </c>
@@ -18925,7 +18929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>1777</v>
       </c>
@@ -18939,7 +18943,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>1780</v>
       </c>
@@ -18953,7 +18957,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>1782</v>
       </c>
@@ -18967,7 +18971,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>1784</v>
       </c>
@@ -18981,7 +18985,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>1786</v>
       </c>
@@ -18995,7 +18999,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>1788</v>
       </c>
@@ -19009,7 +19013,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="762" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>1790</v>
       </c>
@@ -19023,7 +19027,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="763" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>1792</v>
       </c>
@@ -19037,7 +19041,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="764" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>1794</v>
       </c>
@@ -19051,7 +19055,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="765" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>1796</v>
       </c>
@@ -19065,7 +19069,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="766" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>1798</v>
       </c>
@@ -19079,7 +19083,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="767" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>1800</v>
       </c>
@@ -19093,7 +19097,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="768" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>1802</v>
       </c>
@@ -19107,7 +19111,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="769" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>1804</v>
       </c>
@@ -19121,7 +19125,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="770" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>1806</v>
       </c>
@@ -19135,7 +19139,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="771" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>1808</v>
       </c>
@@ -19149,7 +19153,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="772" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>1810</v>
       </c>
@@ -19163,7 +19167,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="773" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>1812</v>
       </c>
@@ -19177,7 +19181,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>1814</v>
       </c>
@@ -19191,7 +19195,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>1816</v>
       </c>
@@ -19205,7 +19209,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="776" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>1818</v>
       </c>
@@ -19219,7 +19223,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="777" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>1820</v>
       </c>
@@ -19233,7 +19237,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="778" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>1822</v>
       </c>
@@ -19247,7 +19251,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="779" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>1824</v>
       </c>
@@ -19261,7 +19265,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="780" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>1826</v>
       </c>
@@ -19275,7 +19279,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="781" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>1828</v>
       </c>
@@ -19289,7 +19293,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="782" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>1830</v>
       </c>
@@ -19303,7 +19307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="783" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>1832</v>
       </c>
@@ -19317,7 +19321,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="784" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>1834</v>
       </c>
@@ -19331,7 +19335,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>1836</v>
       </c>
@@ -19345,7 +19349,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>1838</v>
       </c>
@@ -19362,7 +19366,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>1840</v>
       </c>
@@ -19379,7 +19383,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="788" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>1842</v>
       </c>
@@ -19396,7 +19400,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="789" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>1844</v>
       </c>
@@ -19413,7 +19417,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="790" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>1846</v>
       </c>
@@ -19427,7 +19431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="791" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>1849</v>
       </c>
@@ -19441,7 +19445,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="792" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>1852</v>
       </c>
@@ -19455,7 +19459,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="793" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>1855</v>
       </c>
@@ -19472,7 +19476,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="794" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>1857</v>
       </c>
@@ -19489,7 +19493,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="795" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>1859</v>
       </c>
@@ -19506,7 +19510,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="796" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>1860</v>
       </c>
@@ -19523,7 +19527,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="797" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>1861</v>
       </c>
@@ -19540,7 +19544,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="798" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>1862</v>
       </c>
@@ -19557,7 +19561,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="799" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>1863</v>
       </c>
@@ -19574,7 +19578,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="800" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>1864</v>
       </c>
@@ -19591,7 +19595,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="801" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>1865</v>
       </c>
@@ -19608,7 +19612,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="802" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>1866</v>
       </c>
@@ -19616,7 +19620,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="803" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>1867</v>
       </c>
@@ -19624,7 +19628,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="804" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>1868</v>
       </c>
@@ -19638,7 +19642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="805" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>1871</v>
       </c>
@@ -19652,7 +19656,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="806" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>1873</v>
       </c>
@@ -19666,7 +19670,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="807" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>1875</v>
       </c>
@@ -19680,7 +19684,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="808" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>1877</v>
       </c>
@@ -19694,7 +19698,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="809" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>1879</v>
       </c>
@@ -19708,7 +19712,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="810" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>1881</v>
       </c>
@@ -19722,7 +19726,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="811" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>1883</v>
       </c>
@@ -19736,7 +19740,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="812" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>1885</v>
       </c>
@@ -19750,7 +19754,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="813" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>1887</v>
       </c>
@@ -19764,7 +19768,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="814" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>1889</v>
       </c>
@@ -19778,7 +19782,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="815" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>1891</v>
       </c>
@@ -19792,7 +19796,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="816" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>1893</v>
       </c>
@@ -19806,7 +19810,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="817" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>1895</v>
       </c>
@@ -19820,7 +19824,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="818" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>1897</v>
       </c>
@@ -19834,7 +19838,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="819" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>1899</v>
       </c>
@@ -19848,7 +19852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="820" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>1901</v>
       </c>
@@ -19862,7 +19866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="821" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>1903</v>
       </c>
@@ -19879,7 +19883,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="822" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>1904</v>
       </c>
@@ -19896,7 +19900,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="823" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>1905</v>
       </c>
@@ -19913,7 +19917,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="824" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>1906</v>
       </c>
@@ -19930,7 +19934,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="825" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>1907</v>
       </c>
@@ -19947,7 +19951,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="826" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>1908</v>
       </c>
@@ -19964,7 +19968,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="827" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>1909</v>
       </c>
@@ -19981,7 +19985,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="828" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>1910</v>
       </c>
@@ -19998,7 +20002,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="829" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>1911</v>
       </c>
@@ -20015,7 +20019,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="830" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>1912</v>
       </c>
@@ -20032,7 +20036,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="831" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>1913</v>
       </c>
@@ -20049,7 +20053,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="832" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>1914</v>
       </c>
@@ -20066,7 +20070,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="833" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>1915</v>
       </c>
@@ -20083,7 +20087,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="834" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>1916</v>
       </c>
@@ -20100,7 +20104,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="835" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>1917</v>
       </c>
@@ -20117,7 +20121,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="836" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>1918</v>
       </c>
@@ -20134,7 +20138,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="837" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>1919</v>
       </c>
@@ -20142,7 +20146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="838" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>1920</v>
       </c>
@@ -20150,7 +20154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="839" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>1921</v>
       </c>
@@ -20158,7 +20162,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="840" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>1922</v>
       </c>
@@ -20166,7 +20170,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="841" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>1923</v>
       </c>
@@ -20174,7 +20178,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="842" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>1924</v>
       </c>
@@ -20182,7 +20186,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="843" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>1925</v>
       </c>
@@ -20190,7 +20194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="844" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>1926</v>
       </c>
@@ -20198,7 +20202,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="845" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>1927</v>
       </c>
@@ -20206,7 +20210,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="846" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>1928</v>
       </c>
@@ -20214,7 +20218,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="847" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>1929</v>
       </c>
@@ -20222,7 +20226,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="848" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>1930</v>
       </c>
@@ -20230,7 +20234,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>1931</v>
       </c>
@@ -20238,7 +20242,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>1932</v>
       </c>
@@ -20246,7 +20250,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>1933</v>
       </c>
@@ -20254,7 +20258,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>1934</v>
       </c>
@@ -20262,7 +20266,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>1935</v>
       </c>
@@ -20270,7 +20274,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>1936</v>
       </c>
@@ -20278,7 +20282,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>1937</v>
       </c>
@@ -20286,7 +20290,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>1938</v>
       </c>
@@ -20294,7 +20298,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>1939</v>
       </c>
@@ -20302,7 +20306,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="858" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>1940</v>
       </c>
@@ -20310,7 +20314,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="859" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>1941</v>
       </c>
@@ -20318,7 +20322,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="860" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>1942</v>
       </c>
@@ -20326,7 +20330,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="861" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>1943</v>
       </c>
@@ -20334,7 +20338,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="862" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>1944</v>
       </c>
@@ -20342,7 +20346,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="863" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>1945</v>
       </c>
@@ -20350,7 +20354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="864" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>1946</v>
       </c>
@@ -20358,7 +20362,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>1947</v>
       </c>
@@ -20366,7 +20370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>1948</v>
       </c>
@@ -20374,7 +20378,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>1949</v>
       </c>
@@ -20382,7 +20386,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>1950</v>
       </c>
@@ -20390,7 +20394,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>1951</v>
       </c>
@@ -20398,7 +20402,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>1952</v>
       </c>
@@ -20406,7 +20410,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>1953</v>
       </c>
@@ -20414,7 +20418,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>1954</v>
       </c>
@@ -20422,7 +20426,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>1955</v>
       </c>
@@ -20430,7 +20434,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>1956</v>
       </c>
@@ -20438,7 +20442,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>1957</v>
       </c>
@@ -20446,7 +20450,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>1958</v>
       </c>
@@ -20454,7 +20458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>1959</v>
       </c>
@@ -20462,7 +20466,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>1960</v>
       </c>
@@ -20470,7 +20474,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>1961</v>
       </c>
@@ -20478,7 +20482,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>1962</v>
       </c>
@@ -20486,7 +20490,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="881" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>1963</v>
       </c>
@@ -20494,7 +20498,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="882" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>1964</v>
       </c>
@@ -20502,7 +20506,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="883" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>1965</v>
       </c>
@@ -20510,7 +20514,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>1966</v>
       </c>
@@ -20518,7 +20522,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="885" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>1967</v>
       </c>
@@ -20526,7 +20530,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="886" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>1968</v>
       </c>
@@ -20534,7 +20538,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="887" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>1969</v>
       </c>
@@ -20542,7 +20546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="888" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>1970</v>
       </c>
@@ -20550,7 +20554,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="889" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>1971</v>
       </c>
@@ -20558,7 +20562,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="890" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>1972</v>
       </c>
@@ -20566,7 +20570,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="891" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>1973</v>
       </c>
@@ -20574,7 +20578,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="892" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>1974</v>
       </c>
@@ -20582,7 +20586,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="893" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>1975</v>
       </c>
@@ -20590,7 +20594,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="894" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>1976</v>
       </c>
@@ -20598,7 +20602,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="895" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>1977</v>
       </c>
@@ -20606,7 +20610,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="896" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>1978</v>
       </c>
@@ -20614,7 +20618,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="897" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>1979</v>
       </c>
@@ -20622,7 +20626,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="898" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>1980</v>
       </c>
@@ -20630,7 +20634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="899" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>1981</v>
       </c>
@@ -20638,7 +20642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="900" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>1982</v>
       </c>
@@ -20646,7 +20650,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="901" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>1983</v>
       </c>
@@ -20654,7 +20658,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="902" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>1984</v>
       </c>
@@ -20662,7 +20666,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="903" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>1985</v>
       </c>
@@ -20670,7 +20674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="904" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>1986</v>
       </c>
@@ -20678,7 +20682,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="905" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>1987</v>
       </c>
@@ -20686,7 +20690,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="906" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>1988</v>
       </c>
@@ -20694,7 +20698,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="907" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>1989</v>
       </c>
@@ -20702,7 +20706,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="908" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>1990</v>
       </c>
@@ -20710,7 +20714,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="909" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>1991</v>
       </c>
@@ -20718,7 +20722,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="910" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>1992</v>
       </c>
@@ -20726,7 +20730,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="911" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>1993</v>
       </c>
@@ -20734,7 +20738,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="912" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>1994</v>
       </c>
@@ -20742,7 +20746,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="913" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>1995</v>
       </c>
@@ -20750,7 +20754,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="914" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>1996</v>
       </c>
@@ -20758,7 +20762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="915" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>1997</v>
       </c>
@@ -20766,7 +20770,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="916" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>1998</v>
       </c>
@@ -20774,7 +20778,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="917" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>1999</v>
       </c>
@@ -20782,7 +20786,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="918" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>2000</v>
       </c>
@@ -20790,7 +20794,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="919" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>2001</v>
       </c>
@@ -20798,7 +20802,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="920" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>2002</v>
       </c>
@@ -20806,7 +20810,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="921" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>2003</v>
       </c>
@@ -20814,7 +20818,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="922" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>2004</v>
       </c>
@@ -20822,7 +20826,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="923" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>2005</v>
       </c>
@@ -20830,7 +20834,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="924" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>2006</v>
       </c>
@@ -20838,7 +20842,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="925" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>2007</v>
       </c>
@@ -20846,7 +20850,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="926" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>2008</v>
       </c>
@@ -20854,7 +20858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="927" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>2009</v>
       </c>
@@ -20862,7 +20866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="928" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>2010</v>
       </c>
@@ -20870,7 +20874,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="929" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>2011</v>
       </c>
@@ -20878,7 +20882,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="930" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>2012</v>
       </c>
@@ -20886,7 +20890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="931" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>2013</v>
       </c>
@@ -20894,7 +20898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="932" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>2014</v>
       </c>
@@ -20902,7 +20906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="933" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>2015</v>
       </c>
@@ -20910,7 +20914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="934" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>2016</v>
       </c>
@@ -20918,7 +20922,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="935" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>2017</v>
       </c>
@@ -20926,7 +20930,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="936" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>2018</v>
       </c>
@@ -20934,7 +20938,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="937" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>2019</v>
       </c>
@@ -20942,7 +20946,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="938" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>2020</v>
       </c>
@@ -20950,7 +20954,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="939" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>2021</v>
       </c>
@@ -20958,7 +20962,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="940" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>2022</v>
       </c>
@@ -20966,7 +20970,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="941" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>2023</v>
       </c>
@@ -20974,7 +20978,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="942" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>2024</v>
       </c>
@@ -20982,7 +20986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="943" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>2025</v>
       </c>
@@ -20990,7 +20994,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="944" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>2026</v>
       </c>
@@ -20998,7 +21002,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="945" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>2027</v>
       </c>
@@ -21006,7 +21010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="946" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>2028</v>
       </c>
@@ -21014,7 +21018,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="947" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>2029</v>
       </c>
@@ -21022,7 +21026,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="948" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>2030</v>
       </c>
@@ -21030,7 +21034,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="949" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>2031</v>
       </c>
@@ -21038,7 +21042,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="950" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>2032</v>
       </c>
@@ -21046,7 +21050,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="951" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>2033</v>
       </c>
@@ -21054,7 +21058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="952" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>2034</v>
       </c>
@@ -21062,7 +21066,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="953" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>2035</v>
       </c>
@@ -21070,7 +21074,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="954" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>2036</v>
       </c>
@@ -21078,7 +21082,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="955" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>2037</v>
       </c>
@@ -21086,7 +21090,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="956" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>2038</v>
       </c>
@@ -21094,7 +21098,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="957" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>2039</v>
       </c>
@@ -21102,7 +21106,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="958" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>2040</v>
       </c>
@@ -21110,7 +21114,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="959" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>2041</v>
       </c>
@@ -21118,7 +21122,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="960" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>2042</v>
       </c>
@@ -21126,7 +21130,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="961" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>2043</v>
       </c>
@@ -21134,7 +21138,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="962" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>2044</v>
       </c>
@@ -21142,7 +21146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="963" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>2045</v>
       </c>
@@ -21150,7 +21154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="964" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>2046</v>
       </c>
@@ -21158,7 +21162,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="965" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>2047</v>
       </c>
@@ -21166,7 +21170,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="966" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>2048</v>
       </c>
@@ -21174,7 +21178,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="967" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>2049</v>
       </c>
@@ -21182,7 +21186,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="968" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>2050</v>
       </c>
@@ -21190,7 +21194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="969" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>2051</v>
       </c>
@@ -21198,7 +21202,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="970" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>2052</v>
       </c>
@@ -21206,7 +21210,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="971" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>2053</v>
       </c>
@@ -21214,7 +21218,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="972" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>2054</v>
       </c>
@@ -21222,7 +21226,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="973" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>2055</v>
       </c>
@@ -21230,7 +21234,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="974" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>2056</v>
       </c>
@@ -21238,7 +21242,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="975" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>2057</v>
       </c>
@@ -21246,7 +21250,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="976" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>2058</v>
       </c>
@@ -21254,7 +21258,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="977" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>2059</v>
       </c>
@@ -21262,7 +21266,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="978" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>2060</v>
       </c>
@@ -21270,7 +21274,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="979" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>2061</v>
       </c>
@@ -21278,7 +21282,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="980" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>2062</v>
       </c>
@@ -21286,7 +21290,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="981" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>2063</v>
       </c>
@@ -21294,7 +21298,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="982" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>2064</v>
       </c>
@@ -21302,7 +21306,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="983" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>2065</v>
       </c>
@@ -21310,7 +21314,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="984" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>2066</v>
       </c>
@@ -21318,7 +21322,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="985" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>2067</v>
       </c>
@@ -21326,7 +21330,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="986" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>2068</v>
       </c>
@@ -21334,7 +21338,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="987" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>2069</v>
       </c>
@@ -21342,7 +21346,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="988" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>2070</v>
       </c>
@@ -21350,7 +21354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="989" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>2071</v>
       </c>
@@ -21358,7 +21362,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="990" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>2072</v>
       </c>
@@ -21366,7 +21370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="991" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>2073</v>
       </c>
@@ -21374,7 +21378,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="992" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>2074</v>
       </c>
@@ -21383,7 +21387,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P992" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P992" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="BuffFactory"/>
+        <filter val="CityInstitutionBuilding"/>
+        <filter val="FactoryBuilding7"/>
+        <filter val="FarmBuilding"/>
+        <filter val="Farmfield"/>
+        <filter val="Fertility"/>
+        <filter val="Mall"/>
+        <filter val="MonumentColony"/>
+        <filter val="Multifactory"/>
+        <filter val="OrnamentalBuilding"/>
+        <filter val="PostBoxBuildingWithPublicService"/>
+        <filter val="Product"/>
+        <filter val="PublicServiceBuilding"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:P589">
+      <sortCondition ref="F1:F992"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/config/gui/_Localizations.xlsx
+++ b/data/config/gui/_Localizations.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\Anno 1800\mods\[Addon] Return to the Orient\data\config\gui\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF9DED6-4FE9-4172-9811-CC0F7D9ACCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33028CBA-BF55-4A9B-BC94-F3637DC99A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Localization" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Localization!$A$1:$P$1008</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15678" uniqueCount="2608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15789" uniqueCount="2623">
   <si>
     <t>GUID</t>
   </si>
@@ -7794,61 +7797,106 @@
     <t>The height of decadence to waste precious water in a desert like that, it could be confused for a fata morgana.</t>
   </si>
   <si>
+    <t>Es ist der Gipfel der Dekadenz, in einer solchen Wüste kostbares Wasser zu verschwenden, man könnte es glatt für eine Fata Morgana halten.</t>
+  </si>
+  <si>
     <t>1404001005</t>
   </si>
   <si>
     <t>Some may call it a waste of water but it is some of the few plants that can survive here.</t>
   </si>
   <si>
+    <t>Manche mögen es als Wasserverschwendung bezeichnen, doch es gehört zu den wenigen Pflanzen, die hier überleben können.</t>
+  </si>
+  <si>
     <t>1404001006</t>
   </si>
   <si>
     <t>A beautiful mosaic, just make sure you wear shoes otherwise you will burn yourself.</t>
   </si>
   <si>
+    <t>Ein wunderschönes Mosaik, achte nur darauf, dass du Schuhe trägst, sonst verbrennst du dir die Füße.</t>
+  </si>
+  <si>
     <t>1404001007</t>
   </si>
   <si>
     <t>A piece of an old building that invites visitors to speculate about its history.</t>
   </si>
   <si>
+    <t>Ein Teil eines alten Gebäudes, der Besucher dazu einlädt, über seine Geschichte zu spekulieren.</t>
+  </si>
+  <si>
     <t>1404001008</t>
   </si>
   <si>
     <t>A monument to the resilience of the nomads.</t>
   </si>
   <si>
+    <t>Ein Denkmal für die Widerstandsfähigkeit der Nomaden.</t>
+  </si>
+  <si>
     <t>1404001009</t>
   </si>
   <si>
     <t>A small break from the scorching heat.</t>
   </si>
   <si>
+    <t>Eine kleine Pause von der sengenden Hitze.</t>
+  </si>
+  <si>
     <t>1404001010</t>
   </si>
   <si>
     <t>Popular with nomads for their ease of assembly and disassembly they create a cool space during the day and trap heat at night.</t>
   </si>
   <si>
-    <t>Manche mögen es als Wasserverschwendung bezeichnen, doch es gehört zu den wenigen Pflanzen, die hier überleben können.</t>
-  </si>
-  <si>
-    <t>Ein Teil eines alten Gebäudes, der Besucher dazu einlädt, über seine Geschichte zu spekulieren.</t>
-  </si>
-  <si>
-    <t>Ein Denkmal für die Widerstandsfähigkeit der Nomaden.</t>
-  </si>
-  <si>
-    <t>Eine kleine Pause von der sengenden Hitze.</t>
-  </si>
-  <si>
-    <t>Es ist der Gipfel der Dekadenz, in einer solchen Wüste kostbares Wasser zu verschwenden, man könnte es glatt für eine Fata Morgana halten.</t>
-  </si>
-  <si>
-    <t>Ein wunderschönes Mosaik, achte nur darauf, dass du Schuhe trägst, sonst verbrennst du dir die Füße.</t>
-  </si>
-  <si>
     <t>Sie sind bei Nomaden wegen ihrer einfachen Auf- und Abbauweise beliebt und sorgen tagsüber für angenehme Kühle, während sie nachts die Wärme speichern.</t>
+  </si>
+  <si>
+    <t>1404001011</t>
+  </si>
+  <si>
+    <t>Nomad Needs</t>
+  </si>
+  <si>
+    <t>1404001012</t>
+  </si>
+  <si>
+    <t>Envoy Needs</t>
+  </si>
+  <si>
+    <t>1404001013</t>
+  </si>
+  <si>
+    <t>Into the Desert</t>
+  </si>
+  <si>
+    <t>1404001014</t>
+  </si>
+  <si>
+    <t>Madame Kahina has given you an invitation from the Sultan. This is a rare opportunity, as not many outsiders are allowed to enter the sultanate.</t>
+  </si>
+  <si>
+    <t>1404001015</t>
+  </si>
+  <si>
+    <t>ExpeditionSlot</t>
+  </si>
+  <si>
+    <t>Orient_Unlock</t>
+  </si>
+  <si>
+    <t>Nomaden-Bedürfnisse</t>
+  </si>
+  <si>
+    <t>Gesandten-Bedürfnisse</t>
+  </si>
+  <si>
+    <t>In die Wüste</t>
+  </si>
+  <si>
+    <t>Madame Kahina hat Ihnen eine Einladung des Sultans überreicht. Dies ist eine seltene Gelegenheit, da nur wenige Außenstehende das Sultanat betreten dürfen.</t>
   </si>
 </sst>
 </file>
@@ -8187,10 +8235,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1003"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:P1008"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="16" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -8243,7 +8294,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8293,7 +8344,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -8543,7 +8594,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -8593,7 +8644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -8643,7 +8694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -8743,7 +8794,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -8793,7 +8844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -8843,7 +8894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -8893,7 +8944,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -8943,7 +8994,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -8993,7 +9044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -9043,7 +9094,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -9093,7 +9144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -9143,7 +9194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>76</v>
       </c>
@@ -9193,7 +9244,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -10325,7 +10376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -10375,7 +10426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>129</v>
       </c>
@@ -10425,7 +10476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -10475,7 +10526,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>135</v>
       </c>
@@ -10525,7 +10576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>137</v>
       </c>
@@ -10575,7 +10626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>140</v>
       </c>
@@ -10625,7 +10676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>143</v>
       </c>
@@ -10675,7 +10726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -10725,7 +10776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>149</v>
       </c>
@@ -10775,7 +10826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>151</v>
       </c>
@@ -10825,7 +10876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>154</v>
       </c>
@@ -10875,7 +10926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>157</v>
       </c>
@@ -10925,7 +10976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>160</v>
       </c>
@@ -10975,7 +11026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>164</v>
       </c>
@@ -11025,7 +11076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>168</v>
       </c>
@@ -11075,7 +11126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>171</v>
       </c>
@@ -11125,7 +11176,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -11175,7 +11226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>178</v>
       </c>
@@ -11225,7 +11276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>181</v>
       </c>
@@ -11275,7 +11326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>184</v>
       </c>
@@ -11325,7 +11376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>187</v>
       </c>
@@ -11375,7 +11426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>190</v>
       </c>
@@ -11425,7 +11476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>193</v>
       </c>
@@ -11475,7 +11526,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>196</v>
       </c>
@@ -11525,7 +11576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>199</v>
       </c>
@@ -11575,7 +11626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>202</v>
       </c>
@@ -11625,7 +11676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>205</v>
       </c>
@@ -11675,7 +11726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>208</v>
       </c>
@@ -11725,7 +11776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>211</v>
       </c>
@@ -11775,7 +11826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>214</v>
       </c>
@@ -11825,7 +11876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>217</v>
       </c>
@@ -11875,7 +11926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>220</v>
       </c>
@@ -11925,7 +11976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>223</v>
       </c>
@@ -11975,7 +12026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>226</v>
       </c>
@@ -12025,7 +12076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>229</v>
       </c>
@@ -12075,7 +12126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>232</v>
       </c>
@@ -12125,7 +12176,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>235</v>
       </c>
@@ -12175,7 +12226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>238</v>
       </c>
@@ -12225,7 +12276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>241</v>
       </c>
@@ -12275,7 +12326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>244</v>
       </c>
@@ -12325,7 +12376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>247</v>
       </c>
@@ -12375,7 +12426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>250</v>
       </c>
@@ -12425,7 +12476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>253</v>
       </c>
@@ -12475,7 +12526,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -12525,7 +12576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>259</v>
       </c>
@@ -12575,7 +12626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -12625,7 +12676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>265</v>
       </c>
@@ -12675,7 +12726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>268</v>
       </c>
@@ -12725,7 +12776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>271</v>
       </c>
@@ -12775,7 +12826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>274</v>
       </c>
@@ -12825,7 +12876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>277</v>
       </c>
@@ -12875,7 +12926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>280</v>
       </c>
@@ -12925,7 +12976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>283</v>
       </c>
@@ -12975,7 +13026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>286</v>
       </c>
@@ -13025,7 +13076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>289</v>
       </c>
@@ -13075,7 +13126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>292</v>
       </c>
@@ -13125,7 +13176,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>295</v>
       </c>
@@ -13175,7 +13226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>298</v>
       </c>
@@ -13225,7 +13276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>301</v>
       </c>
@@ -13275,7 +13326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>304</v>
       </c>
@@ -13325,7 +13376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>307</v>
       </c>
@@ -13375,7 +13426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>310</v>
       </c>
@@ -13425,7 +13476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>313</v>
       </c>
@@ -13475,7 +13526,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>316</v>
       </c>
@@ -13525,7 +13576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>319</v>
       </c>
@@ -13575,7 +13626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>322</v>
       </c>
@@ -13625,7 +13676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>325</v>
       </c>
@@ -13675,7 +13726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>328</v>
       </c>
@@ -13725,7 +13776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>331</v>
       </c>
@@ -13775,7 +13826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>334</v>
       </c>
@@ -13825,7 +13876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>337</v>
       </c>
@@ -13875,7 +13926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>340</v>
       </c>
@@ -13925,7 +13976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>343</v>
       </c>
@@ -13975,7 +14026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>346</v>
       </c>
@@ -14025,7 +14076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>349</v>
       </c>
@@ -14075,7 +14126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>352</v>
       </c>
@@ -14125,7 +14176,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>355</v>
       </c>
@@ -14175,7 +14226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>358</v>
       </c>
@@ -14225,7 +14276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>361</v>
       </c>
@@ -14275,7 +14326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>364</v>
       </c>
@@ -14325,7 +14376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>367</v>
       </c>
@@ -14375,7 +14426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>370</v>
       </c>
@@ -14425,7 +14476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>373</v>
       </c>
@@ -14475,7 +14526,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>376</v>
       </c>
@@ -14525,7 +14576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>379</v>
       </c>
@@ -14575,7 +14626,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>382</v>
       </c>
@@ -14625,7 +14676,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>385</v>
       </c>
@@ -14675,7 +14726,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>388</v>
       </c>
@@ -14725,7 +14776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>391</v>
       </c>
@@ -14775,7 +14826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>395</v>
       </c>
@@ -14825,7 +14876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>398</v>
       </c>
@@ -14875,7 +14926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>402</v>
       </c>
@@ -14925,7 +14976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>405</v>
       </c>
@@ -14975,7 +15026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>408</v>
       </c>
@@ -15025,7 +15076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>412</v>
       </c>
@@ -15075,7 +15126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>415</v>
       </c>
@@ -15125,7 +15176,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>419</v>
       </c>
@@ -15175,7 +15226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>422</v>
       </c>
@@ -15225,7 +15276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>425</v>
       </c>
@@ -15275,7 +15326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>428</v>
       </c>
@@ -15325,7 +15376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>431</v>
       </c>
@@ -15375,7 +15426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>435</v>
       </c>
@@ -15425,7 +15476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>439</v>
       </c>
@@ -15475,7 +15526,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>442</v>
       </c>
@@ -15525,7 +15576,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>443</v>
       </c>
@@ -15775,7 +15826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>453</v>
       </c>
@@ -15825,7 +15876,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>457</v>
       </c>
@@ -15875,7 +15926,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>461</v>
       </c>
@@ -15925,7 +15976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>465</v>
       </c>
@@ -15975,7 +16026,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>469</v>
       </c>
@@ -16025,7 +16076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>472</v>
       </c>
@@ -16075,7 +16126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>476</v>
       </c>
@@ -16169,7 +16220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>480</v>
       </c>
@@ -16219,7 +16270,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>482</v>
       </c>
@@ -16269,7 +16320,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>485</v>
       </c>
@@ -16319,7 +16370,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>488</v>
       </c>
@@ -16369,7 +16420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>491</v>
       </c>
@@ -16419,7 +16470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>494</v>
       </c>
@@ -16469,7 +16520,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>498</v>
       </c>
@@ -16669,7 +16720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>508</v>
       </c>
@@ -16719,7 +16770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>512</v>
       </c>
@@ -16869,7 +16920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>521</v>
       </c>
@@ -16919,7 +16970,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>524</v>
       </c>
@@ -16969,7 +17020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>525</v>
       </c>
@@ -17019,7 +17070,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>528</v>
       </c>
@@ -17763,7 +17814,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>559</v>
       </c>
@@ -17813,7 +17864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>564</v>
       </c>
@@ -17863,7 +17914,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>567</v>
       </c>
@@ -17913,7 +17964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>570</v>
       </c>
@@ -17963,7 +18014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>574</v>
       </c>
@@ -18013,7 +18064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>578</v>
       </c>
@@ -18107,7 +18158,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>583</v>
       </c>
@@ -18157,7 +18208,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>584</v>
       </c>
@@ -18307,7 +18358,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>593</v>
       </c>
@@ -18357,7 +18408,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>596</v>
       </c>
@@ -18407,7 +18458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>599</v>
       </c>
@@ -18501,7 +18552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>604</v>
       </c>
@@ -18551,7 +18602,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>607</v>
       </c>
@@ -18645,7 +18696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>611</v>
       </c>
@@ -18695,7 +18746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>614</v>
       </c>
@@ -19489,7 +19540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>650</v>
       </c>
@@ -21827,7 +21878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>705</v>
       </c>
@@ -21877,7 +21928,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>708</v>
       </c>
@@ -21927,7 +21978,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>711</v>
       </c>
@@ -21977,7 +22028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>712</v>
       </c>
@@ -22027,7 +22078,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>714</v>
       </c>
@@ -22077,7 +22128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>717</v>
       </c>
@@ -22127,7 +22178,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>721</v>
       </c>
@@ -22177,7 +22228,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>724</v>
       </c>
@@ -22227,7 +22278,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>727</v>
       </c>
@@ -22277,7 +22328,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>729</v>
       </c>
@@ -22327,7 +22378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>732</v>
       </c>
@@ -22377,7 +22428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>735</v>
       </c>
@@ -22427,7 +22478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>739</v>
       </c>
@@ -22477,7 +22528,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>742</v>
       </c>
@@ -22571,7 +22622,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>747</v>
       </c>
@@ -22797,7 +22848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>754</v>
       </c>
@@ -22847,7 +22898,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>757</v>
       </c>
@@ -22985,7 +23036,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>762</v>
       </c>
@@ -23085,7 +23136,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>768</v>
       </c>
@@ -23135,7 +23186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>771</v>
       </c>
@@ -23185,7 +23236,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>774</v>
       </c>
@@ -23279,7 +23330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>778</v>
       </c>
@@ -23329,7 +23380,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>779</v>
       </c>
@@ -23379,7 +23430,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>781</v>
       </c>
@@ -23429,7 +23480,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>782</v>
       </c>
@@ -23523,7 +23574,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>786</v>
       </c>
@@ -23573,7 +23624,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>790</v>
       </c>
@@ -23623,7 +23674,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>794</v>
       </c>
@@ -23717,7 +23768,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>799</v>
       </c>
@@ -23767,7 +23818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>802</v>
       </c>
@@ -23817,7 +23868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>806</v>
       </c>
@@ -23867,7 +23918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>810</v>
       </c>
@@ -23917,7 +23968,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>813</v>
       </c>
@@ -23967,7 +24018,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>816</v>
       </c>
@@ -24017,7 +24068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>820</v>
       </c>
@@ -24067,7 +24118,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>821</v>
       </c>
@@ -24117,7 +24168,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>822</v>
       </c>
@@ -24167,7 +24218,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>823</v>
       </c>
@@ -24217,7 +24268,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>824</v>
       </c>
@@ -24267,7 +24318,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>825</v>
       </c>
@@ -24317,7 +24368,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>826</v>
       </c>
@@ -24367,7 +24418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>827</v>
       </c>
@@ -24417,7 +24468,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>828</v>
       </c>
@@ -24467,7 +24518,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>829</v>
       </c>
@@ -24517,7 +24568,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>830</v>
       </c>
@@ -24567,7 +24618,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>831</v>
       </c>
@@ -24617,7 +24668,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>832</v>
       </c>
@@ -24667,7 +24718,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>833</v>
       </c>
@@ -25069,7 +25120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>842</v>
       </c>
@@ -25119,7 +25170,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>846</v>
       </c>
@@ -25169,7 +25220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>849</v>
       </c>
@@ -25219,7 +25270,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>852</v>
       </c>
@@ -25269,7 +25320,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>855</v>
       </c>
@@ -25319,7 +25370,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>858</v>
       </c>
@@ -25369,7 +25420,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>861</v>
       </c>
@@ -25419,7 +25470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>862</v>
       </c>
@@ -25469,7 +25520,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>865</v>
       </c>
@@ -25519,7 +25570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>868</v>
       </c>
@@ -25569,7 +25620,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>871</v>
       </c>
@@ -25619,7 +25670,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>872</v>
       </c>
@@ -25669,7 +25720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>873</v>
       </c>
@@ -25763,7 +25814,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>875</v>
       </c>
@@ -25813,7 +25864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>876</v>
       </c>
@@ -25863,7 +25914,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>877</v>
       </c>
@@ -25913,7 +25964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>878</v>
       </c>
@@ -25963,7 +26014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>881</v>
       </c>
@@ -26057,7 +26108,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>883</v>
       </c>
@@ -26107,7 +26158,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>887</v>
       </c>
@@ -26251,7 +26302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>893</v>
       </c>
@@ -26301,7 +26352,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>896</v>
       </c>
@@ -26351,7 +26402,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>899</v>
       </c>
@@ -26595,7 +26646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>910</v>
       </c>
@@ -26695,7 +26746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>919</v>
       </c>
@@ -26795,7 +26846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>927</v>
       </c>
@@ -26895,7 +26946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>935</v>
       </c>
@@ -26995,7 +27046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>943</v>
       </c>
@@ -27095,7 +27146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>951</v>
       </c>
@@ -27195,7 +27246,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>959</v>
       </c>
@@ -27295,7 +27346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>967</v>
       </c>
@@ -27395,7 +27446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>975</v>
       </c>
@@ -27495,7 +27546,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>983</v>
       </c>
@@ -27595,7 +27646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>991</v>
       </c>
@@ -27695,7 +27746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>999</v>
       </c>
@@ -27795,7 +27846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1007</v>
       </c>
@@ -27895,7 +27946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1015</v>
       </c>
@@ -27995,7 +28046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1023</v>
       </c>
@@ -28095,7 +28146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1031</v>
       </c>
@@ -28195,7 +28246,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1039</v>
       </c>
@@ -28295,7 +28346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1047</v>
       </c>
@@ -28395,7 +28446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1055</v>
       </c>
@@ -28495,7 +28546,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1063</v>
       </c>
@@ -28595,7 +28646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1071</v>
       </c>
@@ -28695,7 +28746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1079</v>
       </c>
@@ -28795,7 +28846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1087</v>
       </c>
@@ -28895,7 +28946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1095</v>
       </c>
@@ -28995,7 +29046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1103</v>
       </c>
@@ -29095,7 +29146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1111</v>
       </c>
@@ -29195,7 +29246,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1119</v>
       </c>
@@ -29295,7 +29346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1127</v>
       </c>
@@ -29395,7 +29446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1135</v>
       </c>
@@ -29495,7 +29546,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1143</v>
       </c>
@@ -29595,7 +29646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1151</v>
       </c>
@@ -29695,7 +29746,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1159</v>
       </c>
@@ -29795,7 +29846,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1167</v>
       </c>
@@ -29895,7 +29946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>1175</v>
       </c>
@@ -29995,7 +30046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1183</v>
       </c>
@@ -30095,7 +30146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="449" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1191</v>
       </c>
@@ -30195,7 +30246,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1199</v>
       </c>
@@ -30295,7 +30346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="453" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1207</v>
       </c>
@@ -30395,7 +30446,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1215</v>
       </c>
@@ -30545,7 +30596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1225</v>
       </c>
@@ -30645,7 +30696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1233</v>
       </c>
@@ -30745,7 +30796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1241</v>
       </c>
@@ -30845,7 +30896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="464" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>1249</v>
       </c>
@@ -30945,7 +30996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="466" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1257</v>
       </c>
@@ -31045,7 +31096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="468" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1265</v>
       </c>
@@ -31145,7 +31196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="470" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1273</v>
       </c>
@@ -31245,7 +31296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="472" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1281</v>
       </c>
@@ -31345,7 +31396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1289</v>
       </c>
@@ -31445,7 +31496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1297</v>
       </c>
@@ -31545,7 +31596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="478" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1305</v>
       </c>
@@ -31645,7 +31696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1313</v>
       </c>
@@ -31745,7 +31796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="482" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1321</v>
       </c>
@@ -31845,7 +31896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="484" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1329</v>
       </c>
@@ -31945,7 +31996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>1337</v>
       </c>
@@ -32045,7 +32096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1345</v>
       </c>
@@ -32145,7 +32196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1353</v>
       </c>
@@ -32245,7 +32296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="492" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1361</v>
       </c>
@@ -32345,7 +32396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="494" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1369</v>
       </c>
@@ -32445,7 +32496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1377</v>
       </c>
@@ -32545,7 +32596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>1385</v>
       </c>
@@ -32645,7 +32696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>1393</v>
       </c>
@@ -32745,7 +32796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>1401</v>
       </c>
@@ -32845,7 +32896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1409</v>
       </c>
@@ -32945,7 +32996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>1417</v>
       </c>
@@ -33045,7 +33096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="508" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1425</v>
       </c>
@@ -33145,7 +33196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1433</v>
       </c>
@@ -33245,7 +33296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1441</v>
       </c>
@@ -33345,7 +33396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1449</v>
       </c>
@@ -33445,7 +33496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="516" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>1457</v>
       </c>
@@ -33545,7 +33596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1465</v>
       </c>
@@ -33645,7 +33696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1473</v>
       </c>
@@ -33745,7 +33796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="522" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1481</v>
       </c>
@@ -33845,7 +33896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>1489</v>
       </c>
@@ -33945,7 +33996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1497</v>
       </c>
@@ -34045,7 +34096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>1505</v>
       </c>
@@ -34145,7 +34196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1513</v>
       </c>
@@ -34245,7 +34296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>1521</v>
       </c>
@@ -34345,7 +34396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>1529</v>
       </c>
@@ -34445,7 +34496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>1537</v>
       </c>
@@ -34545,7 +34596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1545</v>
       </c>
@@ -34645,7 +34696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>1553</v>
       </c>
@@ -34745,7 +34796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>1561</v>
       </c>
@@ -34845,7 +34896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>1569</v>
       </c>
@@ -34945,7 +34996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1577</v>
       </c>
@@ -35045,7 +35096,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1585</v>
       </c>
@@ -35145,7 +35196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>1593</v>
       </c>
@@ -35245,7 +35296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>1601</v>
       </c>
@@ -35345,7 +35396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>1609</v>
       </c>
@@ -36483,7 +36534,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>1642</v>
       </c>
@@ -36533,7 +36584,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>1646</v>
       </c>
@@ -36583,7 +36634,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>1649</v>
       </c>
@@ -36633,7 +36684,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>1653</v>
       </c>
@@ -36683,7 +36734,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>1656</v>
       </c>
@@ -36733,7 +36784,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>1659</v>
       </c>
@@ -36883,7 +36934,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>1667</v>
       </c>
@@ -36933,7 +36984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>1670</v>
       </c>
@@ -36983,7 +37034,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>1674</v>
       </c>
@@ -37033,7 +37084,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>1678</v>
       </c>
@@ -37083,7 +37134,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>1681</v>
       </c>
@@ -46621,7 +46672,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="786" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>2025</v>
       </c>
@@ -46671,7 +46722,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="787" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>2028</v>
       </c>
@@ -46721,7 +46772,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="788" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>2031</v>
       </c>
@@ -46771,7 +46822,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="789" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>2034</v>
       </c>
@@ -46971,7 +47022,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="793" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>2046</v>
       </c>
@@ -47021,7 +47072,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="794" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>2051</v>
       </c>
@@ -47071,7 +47122,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="795" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>2056</v>
       </c>
@@ -47121,7 +47172,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="796" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>2060</v>
       </c>
@@ -47171,7 +47222,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="797" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>2063</v>
       </c>
@@ -47221,7 +47272,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="798" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>2067</v>
       </c>
@@ -47271,7 +47322,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="799" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>2071</v>
       </c>
@@ -47321,7 +47372,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="800" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>2075</v>
       </c>
@@ -47371,7 +47422,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="801" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>2079</v>
       </c>
@@ -48359,7 +48410,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="821" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>2120</v>
       </c>
@@ -48409,7 +48460,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="822" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>2123</v>
       </c>
@@ -48459,7 +48510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="823" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>2126</v>
       </c>
@@ -48509,7 +48560,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="824" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>2129</v>
       </c>
@@ -48559,7 +48610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="825" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>2132</v>
       </c>
@@ -48609,7 +48660,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="826" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>2135</v>
       </c>
@@ -48659,7 +48710,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="827" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>2138</v>
       </c>
@@ -48709,7 +48760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="828" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>2141</v>
       </c>
@@ -48759,7 +48810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="829" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>2144</v>
       </c>
@@ -48809,7 +48860,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="830" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>2147</v>
       </c>
@@ -48859,7 +48910,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="831" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>2150</v>
       </c>
@@ -48909,7 +48960,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="832" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>2153</v>
       </c>
@@ -48959,7 +49010,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="833" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>2156</v>
       </c>
@@ -49009,7 +49060,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="834" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>2159</v>
       </c>
@@ -49059,7 +49110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="835" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>2162</v>
       </c>
@@ -49109,7 +49160,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="836" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>2165</v>
       </c>
@@ -51353,7 +51404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="881" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>2258</v>
       </c>
@@ -51403,7 +51454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="882" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>2262</v>
       </c>
@@ -51453,7 +51504,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="883" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>2265</v>
       </c>
@@ -51503,7 +51554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="884" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>2268</v>
       </c>
@@ -51553,7 +51604,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="885" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>2271</v>
       </c>
@@ -51603,7 +51654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="886" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>2274</v>
       </c>
@@ -51653,7 +51704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="887" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>2277</v>
       </c>
@@ -51703,7 +51754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="888" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>2280</v>
       </c>
@@ -51753,7 +51804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="889" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>2283</v>
       </c>
@@ -51803,7 +51854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="890" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>2286</v>
       </c>
@@ -51853,7 +51904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="891" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>2289</v>
       </c>
@@ -51903,7 +51954,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="892" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>2292</v>
       </c>
@@ -51953,7 +52004,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="893" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>2295</v>
       </c>
@@ -52003,7 +52054,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="894" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>2298</v>
       </c>
@@ -52053,7 +52104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="895" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>2301</v>
       </c>
@@ -52103,7 +52154,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="896" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>2304</v>
       </c>
@@ -52153,7 +52204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="897" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>2307</v>
       </c>
@@ -52203,7 +52254,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="898" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>2310</v>
       </c>
@@ -52253,7 +52304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="899" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>2313</v>
       </c>
@@ -52303,7 +52354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="900" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>2316</v>
       </c>
@@ -52353,7 +52404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="901" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>2319</v>
       </c>
@@ -52403,7 +52454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="902" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>2322</v>
       </c>
@@ -52453,7 +52504,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="903" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>2326</v>
       </c>
@@ -52503,7 +52554,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="904" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>2329</v>
       </c>
@@ -52553,7 +52604,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="905" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>2332</v>
       </c>
@@ -52603,7 +52654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="906" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>2336</v>
       </c>
@@ -52653,7 +52704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="907" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>2339</v>
       </c>
@@ -52703,7 +52754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="908" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>2342</v>
       </c>
@@ -52753,7 +52804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="909" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>2345</v>
       </c>
@@ -52803,7 +52854,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="910" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>2348</v>
       </c>
@@ -52853,7 +52904,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="911" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>2351</v>
       </c>
@@ -52903,7 +52954,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="912" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>2354</v>
       </c>
@@ -52953,7 +53004,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="913" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>2358</v>
       </c>
@@ -53003,7 +53054,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="914" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>2361</v>
       </c>
@@ -53053,7 +53104,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="915" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>2365</v>
       </c>
@@ -53103,7 +53154,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="916" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>2369</v>
       </c>
@@ -53153,7 +53204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="917" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>2372</v>
       </c>
@@ -53203,7 +53254,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="918" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>2375</v>
       </c>
@@ -53253,7 +53304,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="919" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>2378</v>
       </c>
@@ -53303,7 +53354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="920" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>2382</v>
       </c>
@@ -53353,7 +53404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="921" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>2385</v>
       </c>
@@ -53403,7 +53454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="922" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>2388</v>
       </c>
@@ -53447,7 +53498,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="923" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>2390</v>
       </c>
@@ -53497,7 +53548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="924" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>2392</v>
       </c>
@@ -53547,7 +53598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="925" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>2395</v>
       </c>
@@ -53597,7 +53648,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="926" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>2398</v>
       </c>
@@ -53647,7 +53698,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="927" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>2401</v>
       </c>
@@ -53697,7 +53748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="928" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>2404</v>
       </c>
@@ -53747,7 +53798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="929" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>2407</v>
       </c>
@@ -53797,7 +53848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="930" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>2410</v>
       </c>
@@ -53847,7 +53898,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="931" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>2413</v>
       </c>
@@ -53897,7 +53948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="932" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>2416</v>
       </c>
@@ -53947,7 +53998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="933" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>2419</v>
       </c>
@@ -53997,7 +54048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="934" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>2422</v>
       </c>
@@ -54047,7 +54098,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="935" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>2425</v>
       </c>
@@ -54097,7 +54148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="936" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>2428</v>
       </c>
@@ -54147,7 +54198,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="937" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>2431</v>
       </c>
@@ -54197,7 +54248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="938" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>2434</v>
       </c>
@@ -54247,7 +54298,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="939" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>2437</v>
       </c>
@@ -54297,7 +54348,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="940" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>2440</v>
       </c>
@@ -54347,7 +54398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="941" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>2443</v>
       </c>
@@ -54397,7 +54448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="942" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>2446</v>
       </c>
@@ -54447,7 +54498,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="943" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>2449</v>
       </c>
@@ -54497,7 +54548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="944" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>2452</v>
       </c>
@@ -54547,7 +54598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="945" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>2455</v>
       </c>
@@ -54597,7 +54648,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="946" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>2458</v>
       </c>
@@ -54647,7 +54698,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="947" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>2461</v>
       </c>
@@ -54697,7 +54748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="948" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>2464</v>
       </c>
@@ -54747,7 +54798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="949" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>2467</v>
       </c>
@@ -54797,7 +54848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="950" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>2470</v>
       </c>
@@ -54847,7 +54898,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="951" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>2473</v>
       </c>
@@ -54897,7 +54948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="952" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>2476</v>
       </c>
@@ -54947,7 +54998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="953" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>2479</v>
       </c>
@@ -54997,7 +55048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="954" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>2482</v>
       </c>
@@ -55047,7 +55098,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="955" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>2485</v>
       </c>
@@ -55097,7 +55148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="956" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>2488</v>
       </c>
@@ -55147,7 +55198,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="957" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>2491</v>
       </c>
@@ -55197,7 +55248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="958" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>2494</v>
       </c>
@@ -55247,7 +55298,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="959" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>2497</v>
       </c>
@@ -55297,7 +55348,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="960" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>2500</v>
       </c>
@@ -55347,7 +55398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="961" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>2503</v>
       </c>
@@ -55397,7 +55448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="962" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>2506</v>
       </c>
@@ -55447,7 +55498,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="963" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>2509</v>
       </c>
@@ -55497,7 +55548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="964" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>2512</v>
       </c>
@@ -55547,7 +55598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="965" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>2515</v>
       </c>
@@ -55747,7 +55798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="969" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>2527</v>
       </c>
@@ -55797,7 +55848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="970" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>2530</v>
       </c>
@@ -57047,7 +57098,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="995" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>2582</v>
       </c>
@@ -57097,7 +57148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="996" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>2584</v>
       </c>
@@ -57107,14 +57158,47 @@
       <c r="C996" t="s">
         <v>2585</v>
       </c>
+      <c r="D996" t="s">
+        <v>23</v>
+      </c>
+      <c r="E996" t="s">
+        <v>23</v>
+      </c>
       <c r="F996" t="s">
         <v>2585</v>
       </c>
+      <c r="G996" t="s">
+        <v>23</v>
+      </c>
       <c r="H996" t="s">
         <v>2586</v>
       </c>
-    </row>
-    <row r="997" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I996" t="s">
+        <v>23</v>
+      </c>
+      <c r="J996" t="s">
+        <v>23</v>
+      </c>
+      <c r="K996" t="s">
+        <v>23</v>
+      </c>
+      <c r="L996" t="s">
+        <v>23</v>
+      </c>
+      <c r="M996" t="s">
+        <v>23</v>
+      </c>
+      <c r="N996" t="s">
+        <v>23</v>
+      </c>
+      <c r="O996" t="s">
+        <v>23</v>
+      </c>
+      <c r="P996" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="997" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>2587</v>
       </c>
@@ -57124,116 +57208,431 @@
       <c r="C997" t="s">
         <v>2588</v>
       </c>
+      <c r="D997" t="s">
+        <v>23</v>
+      </c>
+      <c r="E997" t="s">
+        <v>23</v>
+      </c>
       <c r="F997" t="s">
         <v>2588</v>
       </c>
+      <c r="G997" t="s">
+        <v>23</v>
+      </c>
       <c r="H997" t="s">
-        <v>2605</v>
-      </c>
-    </row>
-    <row r="998" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2589</v>
+      </c>
+      <c r="I997" t="s">
+        <v>23</v>
+      </c>
+      <c r="J997" t="s">
+        <v>23</v>
+      </c>
+      <c r="K997" t="s">
+        <v>23</v>
+      </c>
+      <c r="L997" t="s">
+        <v>23</v>
+      </c>
+      <c r="M997" t="s">
+        <v>23</v>
+      </c>
+      <c r="N997" t="s">
+        <v>23</v>
+      </c>
+      <c r="O997" t="s">
+        <v>23</v>
+      </c>
+      <c r="P997" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="998" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="B998" t="s">
         <v>21</v>
       </c>
       <c r="C998" t="s">
-        <v>2590</v>
+        <v>2591</v>
+      </c>
+      <c r="D998" t="s">
+        <v>23</v>
+      </c>
+      <c r="E998" t="s">
+        <v>23</v>
       </c>
       <c r="F998" t="s">
-        <v>2590</v>
+        <v>2591</v>
+      </c>
+      <c r="G998" t="s">
+        <v>23</v>
       </c>
       <c r="H998" t="s">
-        <v>2601</v>
-      </c>
-    </row>
-    <row r="999" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2592</v>
+      </c>
+      <c r="I998" t="s">
+        <v>23</v>
+      </c>
+      <c r="J998" t="s">
+        <v>23</v>
+      </c>
+      <c r="K998" t="s">
+        <v>23</v>
+      </c>
+      <c r="L998" t="s">
+        <v>23</v>
+      </c>
+      <c r="M998" t="s">
+        <v>23</v>
+      </c>
+      <c r="N998" t="s">
+        <v>23</v>
+      </c>
+      <c r="O998" t="s">
+        <v>23</v>
+      </c>
+      <c r="P998" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="999" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="B999" t="s">
         <v>21</v>
       </c>
       <c r="C999" t="s">
-        <v>2592</v>
+        <v>2594</v>
+      </c>
+      <c r="D999" t="s">
+        <v>23</v>
+      </c>
+      <c r="E999" t="s">
+        <v>23</v>
       </c>
       <c r="F999" t="s">
-        <v>2592</v>
+        <v>2594</v>
+      </c>
+      <c r="G999" t="s">
+        <v>23</v>
       </c>
       <c r="H999" t="s">
-        <v>2606</v>
-      </c>
-    </row>
-    <row r="1000" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2595</v>
+      </c>
+      <c r="I999" t="s">
+        <v>23</v>
+      </c>
+      <c r="J999" t="s">
+        <v>23</v>
+      </c>
+      <c r="K999" t="s">
+        <v>23</v>
+      </c>
+      <c r="L999" t="s">
+        <v>23</v>
+      </c>
+      <c r="M999" t="s">
+        <v>23</v>
+      </c>
+      <c r="N999" t="s">
+        <v>23</v>
+      </c>
+      <c r="O999" t="s">
+        <v>23</v>
+      </c>
+      <c r="P999" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
       <c r="B1000" t="s">
         <v>21</v>
       </c>
       <c r="C1000" t="s">
-        <v>2594</v>
+        <v>2597</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>23</v>
       </c>
       <c r="F1000" t="s">
-        <v>2594</v>
+        <v>2597</v>
+      </c>
+      <c r="G1000" t="s">
+        <v>23</v>
       </c>
       <c r="H1000" t="s">
-        <v>2602</v>
-      </c>
-    </row>
-    <row r="1001" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2598</v>
+      </c>
+      <c r="I1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1000" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1000" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="B1001" t="s">
         <v>21</v>
       </c>
       <c r="C1001" t="s">
-        <v>2596</v>
+        <v>2600</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>23</v>
       </c>
       <c r="F1001" t="s">
-        <v>2596</v>
+        <v>2600</v>
+      </c>
+      <c r="G1001" t="s">
+        <v>23</v>
       </c>
       <c r="H1001" t="s">
-        <v>2603</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2601</v>
+      </c>
+      <c r="I1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1001" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1001" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>2597</v>
+        <v>2602</v>
       </c>
       <c r="B1002" t="s">
         <v>21</v>
       </c>
       <c r="C1002" t="s">
-        <v>2598</v>
+        <v>2603</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>23</v>
       </c>
       <c r="F1002" t="s">
-        <v>2598</v>
+        <v>2603</v>
+      </c>
+      <c r="G1002" t="s">
+        <v>23</v>
       </c>
       <c r="H1002" t="s">
         <v>2604</v>
       </c>
-    </row>
-    <row r="1003" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="I1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1002" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1002" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>2599</v>
+        <v>2605</v>
       </c>
       <c r="B1003" t="s">
         <v>21</v>
       </c>
       <c r="C1003" t="s">
-        <v>2600</v>
+        <v>2606</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>23</v>
       </c>
       <c r="F1003" t="s">
-        <v>2600</v>
+        <v>2606</v>
+      </c>
+      <c r="G1003" t="s">
+        <v>23</v>
       </c>
       <c r="H1003" t="s">
         <v>2607</v>
       </c>
+      <c r="I1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1003" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1003" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1004" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F1004" t="s">
+        <v>2609</v>
+      </c>
+      <c r="H1004" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1005" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F1005" t="s">
+        <v>2611</v>
+      </c>
+      <c r="H1005" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1006" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F1006" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H1006" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1007" t="s">
+        <v>2614</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>2615</v>
+      </c>
+      <c r="F1007" t="s">
+        <v>2615</v>
+      </c>
+      <c r="H1007" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1008" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>2618</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P1008" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="7">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>